--- a/WithoutCapacityConst.xlsx
+++ b/WithoutCapacityConst.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/debdeeppaul/Documents/Procurement/PIDSG25/pricesaa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A81553DE-FD20-6F4D-B34E-60564828C281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3481D74-B4F7-7D47-94AA-FE38E1B52E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5980" yWindow="3940" windowWidth="16380" windowHeight="12220" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3740" yWindow="3940" windowWidth="16380" windowHeight="12220" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="04" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="18">
   <si>
     <t>Hedged price</t>
   </si>
@@ -76,6 +76,24 @@
   </si>
   <si>
     <t>AI-storage</t>
+  </si>
+  <si>
+    <t>Procurement</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>Backlog</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Man</t>
+  </si>
+  <si>
+    <t>Price-SAA</t>
   </si>
 </sst>
 </file>
@@ -120,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -130,6 +148,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -391,7 +412,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="12.6640625" customWidth="1"/>
@@ -928,6 +949,184 @@
         <v>2905.7332921810339</v>
       </c>
     </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F17">
+        <f>B2*D2+C2*E2</f>
+        <v>14367.412551440329</v>
+      </c>
+      <c r="G17">
+        <f>B2*G2+C2*H2</f>
+        <v>17349.538499025341</v>
+      </c>
+    </row>
+    <row r="18" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F18">
+        <f t="shared" ref="F18:F28" si="3">B3*D3+C3*E3</f>
+        <v>7724.5691872427979</v>
+      </c>
+      <c r="G18">
+        <f t="shared" ref="G18:G28" si="4">B3*G3+C3*H3</f>
+        <v>7724.5691872427979</v>
+      </c>
+    </row>
+    <row r="19" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F19">
+        <f t="shared" si="3"/>
+        <v>15264.614806692658</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="4"/>
+        <v>18164.851892462641</v>
+      </c>
+    </row>
+    <row r="20" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F20">
+        <f t="shared" si="3"/>
+        <v>11286.624160710418</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="4"/>
+        <v>14754.93083983106</v>
+      </c>
+    </row>
+    <row r="21" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F21">
+        <f t="shared" si="3"/>
+        <v>11286.624160710418</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="4"/>
+        <v>14421.656662876299</v>
+      </c>
+    </row>
+    <row r="22" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F22">
+        <f t="shared" si="3"/>
+        <v>8373.6103496588712</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="4"/>
+        <v>9000.0690513786012</v>
+      </c>
+    </row>
+    <row r="23" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F23">
+        <f t="shared" si="3"/>
+        <v>8968.5077519379847</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="24" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F24">
+        <f t="shared" si="3"/>
+        <v>10730.581998834603</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="25" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F25">
+        <f t="shared" si="3"/>
+        <v>15154.127931039791</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="26" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F26">
+        <f t="shared" si="3"/>
+        <v>5009.260949016345</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="27" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F27">
+        <f t="shared" si="3"/>
+        <v>8998.1416765727372</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="28" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F28">
+        <f t="shared" si="3"/>
+        <v>7560.7364986884968</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="31" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31">
+        <f>SUM(F17:F28)</f>
+        <v>124724.81202254545</v>
+      </c>
+      <c r="G31">
+        <f>SUM(G17:G28)</f>
+        <v>109981.97415750808</v>
+      </c>
+    </row>
+    <row r="32" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32">
+        <f>0.05*SUM(K2:K13)</f>
+        <v>6487.2618188794722</v>
+      </c>
+      <c r="G32">
+        <f>0.05*SUM(L2:L13)</f>
+        <v>6514.3060349794096</v>
+      </c>
+    </row>
+    <row r="33" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E34" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34">
+        <f>SUM(F31:F33)</f>
+        <v>131212.07384142492</v>
+      </c>
+      <c r="G34">
+        <f>SUM(G31:G33)</f>
+        <v>116496.28019248749</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -936,7 +1135,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34E3220C-D6E8-CA4D-AC53-28C815E97289}">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="12.6640625" customWidth="1"/>
@@ -1005,11 +1204,11 @@
         <v>4886.8312757201647</v>
       </c>
       <c r="H2" s="4">
-        <v>7000</v>
+        <v>5232</v>
       </c>
       <c r="I2">
         <f>SUM(G2:H2)</f>
-        <v>11886.831275720164</v>
+        <v>10118.831275720164</v>
       </c>
       <c r="J2" s="4">
         <v>10314.285714285714</v>
@@ -1087,11 +1286,11 @@
         <v>4886.8312757201647</v>
       </c>
       <c r="H4" s="4">
-        <v>7000</v>
+        <v>3010</v>
       </c>
       <c r="I4">
         <f t="shared" si="1"/>
-        <v>11886.831275720164</v>
+        <v>7896.8312757201647</v>
       </c>
       <c r="J4">
         <v>5625.7573205650187</v>
@@ -1471,6 +1670,184 @@
       </c>
       <c r="L13">
         <v>2905.7332921810339</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F17">
+        <f>B2*D2+C2*E2</f>
+        <v>20896.148657136669</v>
+      </c>
+      <c r="G17">
+        <f>B2*G2+C2*H2</f>
+        <v>14854.518288499024</v>
+      </c>
+    </row>
+    <row r="18" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F18">
+        <f t="shared" ref="F18:F28" si="3">B3*D3+C3*E3</f>
+        <v>7724.5691872427979</v>
+      </c>
+      <c r="G18">
+        <f t="shared" ref="G18:G28" si="4">B3*G3+C3*H3</f>
+        <v>7724.5691872427979</v>
+      </c>
+    </row>
+    <row r="19" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F19">
+        <f t="shared" si="3"/>
+        <v>15264.614806692658</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="4"/>
+        <v>12333.886892462639</v>
+      </c>
+    </row>
+    <row r="20" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F20">
+        <f t="shared" si="3"/>
+        <v>11286.624160710418</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="4"/>
+        <v>14754.93083983106</v>
+      </c>
+    </row>
+    <row r="21" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F21">
+        <f t="shared" si="3"/>
+        <v>11286.624160710418</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="4"/>
+        <v>14421.656662876299</v>
+      </c>
+    </row>
+    <row r="22" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F22">
+        <f t="shared" si="3"/>
+        <v>8373.6103496588712</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="4"/>
+        <v>9000.0690513786012</v>
+      </c>
+    </row>
+    <row r="23" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F23">
+        <f t="shared" si="3"/>
+        <v>8968.5077519379847</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="24" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F24">
+        <f t="shared" si="3"/>
+        <v>10730.581998834603</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="25" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F25">
+        <f t="shared" si="3"/>
+        <v>15154.127931039791</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="26" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F26">
+        <f t="shared" si="3"/>
+        <v>5009.260949016345</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="27" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F27">
+        <f t="shared" si="3"/>
+        <v>8998.1416765727372</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="28" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F28">
+        <f t="shared" si="3"/>
+        <v>7560.7364986884968</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="31" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31">
+        <f>SUM(F17:F28)</f>
+        <v>131253.54812824179</v>
+      </c>
+      <c r="G31">
+        <f>SUM(G17:G28)</f>
+        <v>101655.98894698176</v>
+      </c>
+    </row>
+    <row r="32" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32">
+        <f>0.05*SUM(K2:K13)</f>
+        <v>6191.5549718293805</v>
+      </c>
+      <c r="G32">
+        <f>0.05*SUM(L2:L13)</f>
+        <v>6514.3060349794096</v>
+      </c>
+    </row>
+    <row r="33" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E34" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34">
+        <f>SUM(F31:F33)</f>
+        <v>137445.10310007117</v>
+      </c>
+      <c r="G34">
+        <f>SUM(G31:G33)</f>
+        <v>108170.29498196117</v>
       </c>
     </row>
   </sheetData>
@@ -1481,7 +1858,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A487B8A4-70A8-BF44-BD3B-04E3E6FA5695}">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="12.6640625" customWidth="1"/>
@@ -1550,11 +1927,11 @@
         <v>4886.8312757201647</v>
       </c>
       <c r="H2" s="4">
-        <v>7000</v>
+        <v>5232</v>
       </c>
       <c r="I2">
         <f>SUM(G2:H2)</f>
-        <v>11886.831275720164</v>
+        <v>10118.831275720164</v>
       </c>
       <c r="J2" s="4">
         <v>10314.285714285714</v>
@@ -1591,11 +1968,11 @@
         <v>4886.8312757201647</v>
       </c>
       <c r="H3" s="4">
-        <v>7000</v>
+        <v>3032</v>
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I13" si="1">SUM(G3:H3)</f>
-        <v>11886.831275720164</v>
+        <v>7918.8312757201647</v>
       </c>
       <c r="J3" s="4">
         <v>12000</v>
@@ -1714,11 +2091,11 @@
         <v>4886.8312757201647</v>
       </c>
       <c r="H6" s="4">
-        <v>6657.9218106995604</v>
+        <v>8676</v>
       </c>
       <c r="I6">
         <f t="shared" si="1"/>
-        <v>11544.753086419725</v>
+        <v>13562.831275720164</v>
       </c>
       <c r="J6">
         <v>6493.9081133646077</v>
@@ -2016,6 +2393,184 @@
       </c>
       <c r="L13">
         <v>2905.7332921810339</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F17">
+        <f>B2*D2+C2*E2</f>
+        <v>20896.148657136669</v>
+      </c>
+      <c r="G17">
+        <f>B2*G2+C2*H2</f>
+        <v>14854.518288499024</v>
+      </c>
+    </row>
+    <row r="18" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F18">
+        <f t="shared" ref="F18:F28" si="3">B3*D3+C3*E3</f>
+        <v>7724.5691872427979</v>
+      </c>
+      <c r="G18">
+        <f t="shared" ref="G18:G28" si="4">B3*G3+C3*H3</f>
+        <v>7724.5691872427979</v>
+      </c>
+    </row>
+    <row r="19" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F19">
+        <f t="shared" si="3"/>
+        <v>15264.614806692658</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="4"/>
+        <v>18164.851892462641</v>
+      </c>
+    </row>
+    <row r="20" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F20">
+        <f t="shared" si="3"/>
+        <v>11286.624160710418</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="4"/>
+        <v>14754.93083983106</v>
+      </c>
+    </row>
+    <row r="21" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F21">
+        <f t="shared" si="3"/>
+        <v>11286.624160710418</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="4"/>
+        <v>16387.795892462636</v>
+      </c>
+    </row>
+    <row r="22" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F22">
+        <f t="shared" si="3"/>
+        <v>8373.6103496588712</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="4"/>
+        <v>9000.0690513786012</v>
+      </c>
+    </row>
+    <row r="23" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F23">
+        <f t="shared" si="3"/>
+        <v>8968.5077519379847</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="24" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F24">
+        <f t="shared" si="3"/>
+        <v>10730.581998834603</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="25" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F25">
+        <f t="shared" si="3"/>
+        <v>15154.127931039791</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="26" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F26">
+        <f t="shared" si="3"/>
+        <v>5009.260949016345</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="27" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F27">
+        <f t="shared" si="3"/>
+        <v>8998.1416765727372</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="28" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F28">
+        <f t="shared" si="3"/>
+        <v>7560.7364986884968</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="31" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31">
+        <f>SUM(F17:F28)</f>
+        <v>131253.54812824179</v>
+      </c>
+      <c r="G31">
+        <f>SUM(G17:G28)</f>
+        <v>109453.0931765681</v>
+      </c>
+    </row>
+    <row r="32" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32">
+        <f>0.05*SUM(K2:K13)</f>
+        <v>4148.0567261119495</v>
+      </c>
+      <c r="G32">
+        <f>0.05*SUM(L2:L13)</f>
+        <v>6514.3060349794096</v>
+      </c>
+    </row>
+    <row r="33" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E34" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34">
+        <f>SUM(F31:F33)</f>
+        <v>135401.60485435373</v>
+      </c>
+      <c r="G34">
+        <f>SUM(G31:G33)</f>
+        <v>115967.39921154751</v>
       </c>
     </row>
   </sheetData>
@@ -2026,7 +2581,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7E44A41-3F86-B94E-AB4B-AA39DD02AB15}">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="12.6640625" customWidth="1"/>
@@ -2094,12 +2649,12 @@
       <c r="G2" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="H2" s="4">
-        <v>7000</v>
+      <c r="H2" s="5">
+        <v>2483.1669423159556</v>
       </c>
       <c r="I2">
         <f>SUM(G2:H2)</f>
-        <v>11886.831275720164</v>
+        <v>7369.9982180361203</v>
       </c>
       <c r="J2" s="4">
         <v>10314.285714285714</v>
@@ -2135,12 +2690,12 @@
       <c r="G3" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="H3" s="4">
-        <v>7000</v>
+      <c r="H3" s="5">
+        <v>0</v>
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I13" si="1">SUM(G3:H3)</f>
-        <v>11886.831275720164</v>
+        <v>4886.8312757201647</v>
       </c>
       <c r="J3" s="4">
         <v>12000</v>
@@ -2176,12 +2731,12 @@
       <c r="G4" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="H4" s="4">
-        <v>7000</v>
+      <c r="H4" s="5">
+        <v>2545.222790928924</v>
       </c>
       <c r="I4">
         <f t="shared" si="1"/>
-        <v>11886.831275720164</v>
+        <v>7432.0540666490888</v>
       </c>
       <c r="J4" s="4">
         <v>9828.5714285714294</v>
@@ -2217,12 +2772,12 @@
       <c r="G5" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="H5" s="4">
-        <v>7000</v>
+      <c r="H5">
+        <v>6307.6131687242596</v>
       </c>
       <c r="I5">
         <f t="shared" si="1"/>
-        <v>11886.831275720164</v>
+        <v>11194.444444444423</v>
       </c>
       <c r="J5">
         <v>6433.9826158977739</v>
@@ -2258,12 +2813,12 @@
       <c r="G6" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="H6" s="4">
-        <v>6657.9218106995604</v>
+      <c r="H6">
+        <v>7000</v>
       </c>
       <c r="I6">
         <f t="shared" si="1"/>
-        <v>11544.753086419725</v>
+        <v>11886.831275720164</v>
       </c>
       <c r="J6">
         <v>6493.9081133646077</v>
@@ -2299,12 +2854,12 @@
       <c r="G7" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="H7" s="4">
-        <v>3279.3186831275698</v>
+      <c r="H7">
+        <v>0</v>
       </c>
       <c r="I7">
         <f t="shared" si="1"/>
-        <v>8166.1499588477345</v>
+        <v>4886.8312757201647</v>
       </c>
       <c r="J7">
         <v>6071.2326312903115</v>
@@ -2340,7 +2895,7 @@
       <c r="G8" s="2">
         <v>2764.9176954732511</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
@@ -2381,12 +2936,12 @@
       <c r="G9" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="H9" s="4">
-        <v>0</v>
+      <c r="H9">
+        <v>585.00395061726795</v>
       </c>
       <c r="I9">
         <f t="shared" si="1"/>
-        <v>2767.3611111111113</v>
+        <v>3352.3650617283793</v>
       </c>
       <c r="J9">
         <v>6026.4848889003415</v>
@@ -2422,7 +2977,7 @@
       <c r="G10" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
@@ -2463,7 +3018,7 @@
       <c r="G11" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
@@ -2504,7 +3059,7 @@
       <c r="G12" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
@@ -2545,7 +3100,7 @@
       <c r="G13" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
@@ -2561,6 +3116,184 @@
       </c>
       <c r="L13">
         <v>2905.7332921810339</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F17">
+        <f>B2*D2+C2*E2</f>
+        <v>20896.148657136669</v>
+      </c>
+      <c r="G17">
+        <f>B2*G2+C2*H2</f>
+        <v>10975.336142410484</v>
+      </c>
+    </row>
+    <row r="18" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F18">
+        <f t="shared" ref="F18:F28" si="3">B3*D3+C3*E3</f>
+        <v>7724.5691872427979</v>
+      </c>
+      <c r="G18">
+        <f t="shared" ref="G18:G28" si="4">B3*G3+C3*H3</f>
+        <v>7724.5691872427979</v>
+      </c>
+    </row>
+    <row r="19" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F19">
+        <f t="shared" si="3"/>
+        <v>22004.599980274761</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="4"/>
+        <v>11654.663925322006</v>
+      </c>
+    </row>
+    <row r="20" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F20">
+        <f t="shared" si="3"/>
+        <v>11286.624160710418</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="4"/>
+        <v>14080.363859107627</v>
+      </c>
+    </row>
+    <row r="21" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F21">
+        <f t="shared" si="3"/>
+        <v>11286.624160710418</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="4"/>
+        <v>14754.93083983106</v>
+      </c>
+    </row>
+    <row r="22" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F22">
+        <f t="shared" si="3"/>
+        <v>8373.6103496588712</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="4"/>
+        <v>7935.0887345679021</v>
+      </c>
+    </row>
+    <row r="23" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F23">
+        <f t="shared" si="3"/>
+        <v>8968.5077519379847</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="24" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F24">
+        <f t="shared" si="3"/>
+        <v>10730.581998834603</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="4"/>
+        <v>5767.5198343467655</v>
+      </c>
+    </row>
+    <row r="25" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F25">
+        <f t="shared" si="3"/>
+        <v>15154.127931039791</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="26" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F26">
+        <f t="shared" si="3"/>
+        <v>5009.260949016345</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="27" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F27">
+        <f t="shared" si="3"/>
+        <v>8998.1416765727372</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="28" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F28">
+        <f t="shared" si="3"/>
+        <v>7560.7364986884968</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="31" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31">
+        <f>SUM(F17:F28)</f>
+        <v>137993.53330182392</v>
+      </c>
+      <c r="G31">
+        <f>SUM(G17:G28)</f>
+        <v>96697.770876738097</v>
+      </c>
+    </row>
+    <row r="32" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32">
+        <f>0.05*SUM(K2:K13)</f>
+        <v>4352.6608420088032</v>
+      </c>
+      <c r="G32">
+        <f>0.05*SUM(L2:L13)</f>
+        <v>6514.3060349794096</v>
+      </c>
+    </row>
+    <row r="33" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E34" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34">
+        <f>SUM(F31:F33)</f>
+        <v>142346.19414383272</v>
+      </c>
+      <c r="G34">
+        <f>SUM(G31:G33)</f>
+        <v>103212.07691171751</v>
       </c>
     </row>
   </sheetData>
@@ -2571,7 +3304,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42DA7594-E291-8048-9A99-303698ABB733}">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="12.6640625" customWidth="1"/>
@@ -3096,6 +3829,184 @@
         <v>2905.7332921810339</v>
       </c>
     </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F17">
+        <f>B2*D2+C2*E2</f>
+        <v>20896.148657136669</v>
+      </c>
+      <c r="G17">
+        <f>B2*G2+C2*H2</f>
+        <v>20896.148657136669</v>
+      </c>
+    </row>
+    <row r="18" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F18">
+        <f t="shared" ref="F18:F28" si="2">B3*D3+C3*E3</f>
+        <v>7724.5691872427979</v>
+      </c>
+      <c r="G18">
+        <f t="shared" ref="G18:G28" si="3">B3*G3+C3*H3</f>
+        <v>7724.5691872427979</v>
+      </c>
+    </row>
+    <row r="19" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F19">
+        <f t="shared" si="2"/>
+        <v>22004.599980274761</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="3"/>
+        <v>22004.599980274761</v>
+      </c>
+    </row>
+    <row r="20" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F20">
+        <f t="shared" si="2"/>
+        <v>15087.875680327363</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="3"/>
+        <v>15087.875680327363</v>
+      </c>
+    </row>
+    <row r="21" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F21">
+        <f t="shared" si="2"/>
+        <v>15087.875680327363</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="3"/>
+        <v>22549.036102988954</v>
+      </c>
+    </row>
+    <row r="22" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F22">
+        <f t="shared" si="2"/>
+        <v>9382.2124508802881</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="3"/>
+        <v>12806.437418778429</v>
+      </c>
+    </row>
+    <row r="23" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F23">
+        <f t="shared" si="2"/>
+        <v>22926.580730897007</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="3"/>
+        <v>30594.569444444445</v>
+      </c>
+    </row>
+    <row r="24" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F24">
+        <f t="shared" si="2"/>
+        <v>17400.951982633287</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="3"/>
+        <v>10075.257124434422</v>
+      </c>
+    </row>
+    <row r="25" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F25">
+        <f t="shared" si="2"/>
+        <v>19582.449804878968</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="3"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="26" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F26">
+        <f t="shared" si="2"/>
+        <v>5737.1248804581701</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="3"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="27" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F27">
+        <f t="shared" si="2"/>
+        <v>11894.361210045459</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="3"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="28" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F28">
+        <f t="shared" si="2"/>
+        <v>10402.172375399885</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="3"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="31" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31">
+        <f>SUM(F17:F28)</f>
+        <v>178126.92262050201</v>
+      </c>
+      <c r="G31">
+        <f>SUM(G17:G28)</f>
+        <v>160782.7322787554</v>
+      </c>
+    </row>
+    <row r="32" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32">
+        <f>0.05*SUM(K2:K13)</f>
+        <v>1975.7142857142856</v>
+      </c>
+      <c r="G32">
+        <f>0.05*SUM(L2:L13)</f>
+        <v>6514.3060349794096</v>
+      </c>
+    </row>
+    <row r="33" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E34" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34">
+        <f>SUM(F31:F33)</f>
+        <v>180102.6369062163</v>
+      </c>
+      <c r="G34">
+        <f>SUM(G31:G33)</f>
+        <v>167297.03831373481</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/WithoutCapacityConst.xlsx
+++ b/WithoutCapacityConst.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jppanasonic-my.sharepoint.com/personal/debdeep_paul_sg_panasonic_com/Documents/ドキュメント/ProcurementPIDSG/Forecast25/250925/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/debdeeppaul/Documents/Procurement/PIDSG25/pricesaa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{C3481D74-B4F7-7D47-94AA-FE38E1B52E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFFAA6C1-E3BF-4235-9B80-8460360EE0FF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CAA6C4D-3BFE-1148-B510-0F31C84564BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6560" yWindow="5040" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="04" sheetId="1" r:id="rId1"/>
+    <sheet name="04" sheetId="11" r:id="rId1"/>
     <sheet name="05" sheetId="9" r:id="rId2"/>
-    <sheet name="06" sheetId="7" r:id="rId3"/>
-    <sheet name="07" sheetId="8" r:id="rId4"/>
-    <sheet name="08" sheetId="6" r:id="rId5"/>
+    <sheet name="05Asol" sheetId="13" r:id="rId3"/>
+    <sheet name="06" sheetId="7" r:id="rId4"/>
+    <sheet name="07" sheetId="8" r:id="rId5"/>
+    <sheet name="08" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="10" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="26">
   <si>
     <t>Hedged price</t>
   </si>
@@ -104,6 +106,21 @@
   <si>
     <t>Unhed</t>
   </si>
+  <si>
+    <t>Jul</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>Jun</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>Apr</t>
+  </si>
 </sst>
 </file>
 
@@ -147,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -159,6 +176,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -420,15 +440,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L34"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF235A62-87F9-6044-90ED-F19AB9A4C355}">
+  <dimension ref="A1:L40"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="12.6328125" customWidth="1"/>
-    <col min="5" max="5" width="15.6328125" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="41" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
@@ -466,15 +486,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>45772</v>
       </c>
       <c r="B2">
-        <v>1.5288157894736842</v>
+        <v>47.552286315789345</v>
       </c>
       <c r="C2">
-        <v>1.4112105263157895</v>
+        <v>43.894292210526316</v>
       </c>
       <c r="D2" s="2">
         <v>4886.8312757201647</v>
@@ -489,7 +509,7 @@
       <c r="G2" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2">
         <v>7000</v>
       </c>
       <c r="I2">
@@ -497,23 +517,23 @@
         <v>11886.831275720164</v>
       </c>
       <c r="J2">
-        <v>5195.1035206425595</v>
+        <v>9773.6625514403295</v>
       </c>
       <c r="K2">
         <f>F2-J2</f>
-        <v>4578.55903079777</v>
+        <v>0</v>
       </c>
       <c r="L2">
         <f>I2-J2</f>
-        <v>6691.7277550776043</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+        <v>2113.1687242798344</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>45802</v>
       </c>
       <c r="B3">
-        <v>1.5806907894736841</v>
+        <v>49.165806315789467</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -531,7 +551,7 @@
       <c r="G3" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3">
         <v>7000</v>
       </c>
       <c r="I3">
@@ -539,26 +559,26 @@
         <v>11886.831275720164</v>
       </c>
       <c r="J3">
-        <v>5907.1382972953343</v>
+        <v>5079.7325102880659</v>
       </c>
       <c r="K3">
         <f>K2+F3-J3</f>
-        <v>3751.1532437905025</v>
+        <v>0</v>
       </c>
       <c r="L3">
         <f>L2+I3-J3</f>
-        <v>12671.420733502435</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+        <v>8920.2674897119323</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>45833</v>
       </c>
       <c r="B4">
-        <v>1.6237697368421053</v>
+        <v>50.505733894736842</v>
       </c>
       <c r="C4">
-        <v>1.4613947368421052</v>
+        <v>45.455221894736837</v>
       </c>
       <c r="D4" s="2">
         <v>4886.8312757201647</v>
@@ -573,7 +593,7 @@
       <c r="G4" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4">
         <v>7000</v>
       </c>
       <c r="I4">
@@ -581,26 +601,26 @@
         <v>11886.831275720164</v>
       </c>
       <c r="J4">
-        <v>5625.7573205650187</v>
+        <v>9902.2633744855975</v>
       </c>
       <c r="K4">
         <f t="shared" ref="K4:K13" si="2">K3+F4-J4</f>
-        <v>8027.6592977110813</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <f>L3+I4-J4</f>
-        <v>18932.494688657578</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+        <v>10904.835390946499</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>45863</v>
       </c>
       <c r="B5">
-        <v>1.6237697368421053</v>
+        <v>50.505733894736842</v>
       </c>
       <c r="C5">
-        <v>0.97426315789473683</v>
+        <v>30.303481263157895</v>
       </c>
       <c r="D5" s="2">
         <v>4886.8312757201647</v>
@@ -615,7 +635,7 @@
       <c r="G5" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5">
         <v>7000</v>
       </c>
       <c r="I5">
@@ -623,26 +643,26 @@
         <v>11886.831275720164</v>
       </c>
       <c r="J5">
-        <v>6433.9826158977739</v>
+        <v>8326.9032921810704</v>
       </c>
       <c r="K5">
         <f t="shared" si="2"/>
-        <v>9920.5799739943777</v>
+        <v>0</v>
       </c>
       <c r="L5">
         <f t="shared" ref="L5:L12" si="3">L4+I5-J5</f>
-        <v>24385.343348479968</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+        <v>14464.763374485594</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>45894</v>
       </c>
       <c r="B6">
-        <v>1.6237697368421053</v>
+        <v>50.505733894736842</v>
       </c>
       <c r="C6">
-        <v>0.97426315789473683</v>
+        <v>30.303481263157895</v>
       </c>
       <c r="D6" s="2">
         <v>4886.8312757201647</v>
@@ -657,7 +677,7 @@
       <c r="G6" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6">
         <v>6657.9218106995604</v>
       </c>
       <c r="I6">
@@ -665,26 +685,26 @@
         <v>11544.753086419725</v>
       </c>
       <c r="J6">
-        <v>6493.9081133646077</v>
+        <v>8326.9032921810704</v>
       </c>
       <c r="K6">
         <f t="shared" si="2"/>
-        <v>11753.575152810841</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <f t="shared" si="3"/>
-        <v>29436.188321535086</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+        <v>17682.613168724245</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>45925</v>
       </c>
       <c r="B7">
-        <v>1.6237697368421053</v>
+        <v>50.505733894736842</v>
       </c>
       <c r="C7">
-        <v>0.32475657894736842</v>
+        <v>10.101228631578946</v>
       </c>
       <c r="D7" s="2">
         <v>4886.8312757201647</v>
@@ -699,7 +719,7 @@
       <c r="G7" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7">
         <v>3279.3186831275698</v>
       </c>
       <c r="I7">
@@ -707,26 +727,26 @@
         <v>8166.1499588477345</v>
       </c>
       <c r="J7">
-        <v>6071.2326312903115</v>
+        <v>6237.1399176954737</v>
       </c>
       <c r="K7">
         <f t="shared" si="2"/>
-        <v>11919.482439216003</v>
+        <v>0</v>
       </c>
       <c r="L7">
         <f t="shared" si="3"/>
-        <v>31531.105649092511</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+        <v>19611.623209876507</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>45955</v>
       </c>
       <c r="B8">
-        <v>1.7219534883720931</v>
+        <v>53.559641302325581</v>
       </c>
       <c r="C8">
-        <v>1.7219534883720931</v>
+        <v>53.559641302325581</v>
       </c>
       <c r="D8" s="2">
         <v>2764.9176954732511</v>
@@ -741,7 +761,7 @@
       <c r="G8" s="2">
         <v>2764.9176954732511</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
@@ -749,26 +769,26 @@
         <v>2764.9176954732511</v>
       </c>
       <c r="J8">
-        <v>6403.8158313631438</v>
+        <v>5208.333333333333</v>
       </c>
       <c r="K8">
         <f t="shared" si="2"/>
-        <v>10723.999941186194</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <f t="shared" si="3"/>
-        <v>27892.207513202622</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>17168.207572016425</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>45986</v>
       </c>
       <c r="B9">
-        <v>1.720433105627585</v>
+        <v>53.512351317440405</v>
       </c>
       <c r="C9">
-        <v>1.720433105627585</v>
+        <v>53.512351317440405</v>
       </c>
       <c r="D9" s="2">
         <v>2767.3611111111113</v>
@@ -783,7 +803,7 @@
       <c r="G9" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
@@ -791,26 +811,26 @@
         <v>2767.3611111111113</v>
       </c>
       <c r="J9">
-        <v>6026.4848889003415</v>
+        <v>6237.1399176954737</v>
       </c>
       <c r="K9">
         <f t="shared" si="2"/>
-        <v>10934.654969981326</v>
+        <v>0</v>
       </c>
       <c r="L9">
         <f t="shared" si="3"/>
-        <v>24633.083735413391</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+        <v>13698.428765432065</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>46016</v>
       </c>
       <c r="B10">
-        <v>1.720433105627585</v>
+        <v>53.512351317440405</v>
       </c>
       <c r="C10">
-        <v>2.2939030624099632</v>
+        <v>71.349560853199492</v>
       </c>
       <c r="D10" s="2">
         <v>2767.3611111111113</v>
@@ -825,7 +845,7 @@
       <c r="G10" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
@@ -833,26 +853,26 @@
         <v>2767.3611111111113</v>
       </c>
       <c r="J10">
-        <v>4479.7985738060161</v>
+        <v>7298.0967078189306</v>
       </c>
       <c r="K10">
         <f t="shared" si="2"/>
-        <v>13752.953103994241</v>
+        <v>0</v>
       </c>
       <c r="L10">
         <f t="shared" si="3"/>
-        <v>22920.646272718484</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+        <v>9167.6931687242432</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>46047</v>
       </c>
       <c r="B11">
-        <v>1.720433105627585</v>
+        <v>53.512351317440405</v>
       </c>
       <c r="C11">
-        <v>0.28673497839118917</v>
+        <v>8.9186047678795468</v>
       </c>
       <c r="D11" s="2">
         <v>2767.3611111111113</v>
@@ -867,7 +887,7 @@
       <c r="G11" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
@@ -875,26 +895,26 @@
         <v>2767.3611111111113</v>
       </c>
       <c r="J11">
-        <v>4284.164832400751</v>
+        <v>3632.9732510288068</v>
       </c>
       <c r="K11">
         <f t="shared" si="2"/>
-        <v>13101.761522622295</v>
+        <v>0</v>
       </c>
       <c r="L11">
         <f t="shared" si="3"/>
-        <v>21403.842551428843</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+        <v>8302.0810288065477</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>46078</v>
       </c>
       <c r="B12">
-        <v>1.720433105627585</v>
+        <v>53.512351317440405</v>
       </c>
       <c r="C12">
-        <v>1.4336865095961708</v>
+        <v>44.593385194479296</v>
       </c>
       <c r="D12" s="2">
         <v>2767.3611111111113</v>
@@ -909,7 +929,7 @@
       <c r="G12" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
@@ -917,26 +937,26 @@
         <v>2767.3611111111113</v>
       </c>
       <c r="J12">
-        <v>3874.8158713185621</v>
+        <v>5722.7366255144034</v>
       </c>
       <c r="K12">
         <f t="shared" si="2"/>
-        <v>14949.682276818137</v>
+        <v>0</v>
       </c>
       <c r="L12">
         <f t="shared" si="3"/>
-        <v>20296.387791221394</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+        <v>5346.7055144032556</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>46106</v>
       </c>
       <c r="B13">
-        <v>1.720433105627585</v>
+        <v>53.512351317440405</v>
       </c>
       <c r="C13">
-        <v>1.1469515312049816</v>
+        <v>35.674780426599746</v>
       </c>
       <c r="D13" s="2">
         <v>2767.3611111111113</v>
@@ -951,7 +971,7 @@
       <c r="G13" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
@@ -959,18 +979,36 @@
         <v>2767.3611111111113</v>
       </c>
       <c r="J13">
-        <v>3826.840185484803</v>
+        <v>5208.333333333333</v>
       </c>
       <c r="K13">
         <f t="shared" si="2"/>
-        <v>16331.175424666666</v>
+        <v>0</v>
       </c>
       <c r="L13">
         <f>L12+I13-J13</f>
-        <v>19236.908716847702</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+        <v>2905.7332921810339</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B15">
+        <f>B2*31.104</f>
+        <v>1479.0663135663117</v>
+      </c>
+      <c r="C15">
+        <f>C2*31.104</f>
+        <v>1365.2880649162105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B16">
+        <f t="shared" ref="B16:C26" si="4">B3*31.104</f>
+        <v>1529.2532396463155</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="F16" t="s">
         <v>16</v>
       </c>
@@ -978,161 +1016,236 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B17">
+        <f t="shared" si="4"/>
+        <v>1570.9303470618947</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="4"/>
+        <v>1413.8392218138945</v>
+      </c>
       <c r="F17">
         <f>B2*D2+C2*E2</f>
-        <v>14367.412551440329</v>
+        <v>446883.99999999942</v>
       </c>
       <c r="G17">
         <f>B2*G2+C2*H2</f>
-        <v>17349.538499025341</v>
-      </c>
-    </row>
-    <row r="18" spans="5:8" x14ac:dyDescent="0.35">
+        <v>539640.04547368363</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B18">
+        <f t="shared" si="4"/>
+        <v>1570.9303470618947</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="4"/>
+        <v>942.55948120926314</v>
+      </c>
       <c r="F18">
-        <f t="shared" ref="F18:F28" si="4">B3*D3+C3*E3</f>
-        <v>7724.5691872427979</v>
+        <f t="shared" ref="F18:F28" si="5">B3*D3+C3*E3</f>
+        <v>240264.99999999997</v>
       </c>
       <c r="G18">
-        <f t="shared" ref="G18:G28" si="5">B3*G3+C3*H3</f>
-        <v>7724.5691872427979</v>
-      </c>
-    </row>
-    <row r="19" spans="5:8" x14ac:dyDescent="0.35">
+        <f t="shared" ref="G18:G28" si="6">B3*G3+C3*H3</f>
+        <v>240264.99999999997</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B19">
+        <f t="shared" si="4"/>
+        <v>1570.9303470618947</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="4"/>
+        <v>942.55948120926314</v>
+      </c>
       <c r="F19">
+        <f t="shared" si="5"/>
+        <v>474790.57894736843</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="6"/>
+        <v>564999.55326315784</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B20">
         <f t="shared" si="4"/>
-        <v>15264.614806692658</v>
-      </c>
-      <c r="G19">
+        <v>1570.9303470618947</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="4"/>
+        <v>314.18861535663154</v>
+      </c>
+      <c r="F20">
         <f t="shared" si="5"/>
-        <v>18164.851892462641</v>
-      </c>
-    </row>
-    <row r="20" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="F20">
+        <v>351059.15789473685</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="6"/>
+        <v>458937.36884210526</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B21">
         <f t="shared" si="4"/>
-        <v>11286.624160710418</v>
-      </c>
-      <c r="G20">
+        <v>1665.9190830675348</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="4"/>
+        <v>1665.9190830675348</v>
+      </c>
+      <c r="F21">
         <f t="shared" si="5"/>
-        <v>14754.93083983106</v>
-      </c>
-    </row>
-    <row r="21" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="F21">
+        <v>351059.15789473685</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="6"/>
+        <v>448571.20884210442</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B22">
         <f t="shared" si="4"/>
-        <v>11286.624160710418</v>
-      </c>
-      <c r="G21">
+        <v>1664.4481753776663</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="4"/>
+        <v>1664.4481753776663</v>
+      </c>
+      <c r="F22">
         <f t="shared" si="5"/>
-        <v>14421.656662876299</v>
-      </c>
-    </row>
-    <row r="22" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="F22">
+        <v>260452.77631578947</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="6"/>
+        <v>279938.14777407999</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B23">
         <f t="shared" si="4"/>
-        <v>8373.6103496588712</v>
-      </c>
-      <c r="G22">
+        <v>1664.4481753776663</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="4"/>
+        <v>2219.256740777917</v>
+      </c>
+      <c r="F23">
         <f t="shared" si="5"/>
-        <v>9000.0690513786012</v>
-      </c>
-    </row>
-    <row r="23" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="F23">
+        <v>278956.46511627908</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="6"/>
+        <v>148088</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B24">
         <f t="shared" si="4"/>
-        <v>8968.5077519379847</v>
-      </c>
-      <c r="G23">
+        <v>1664.4481753776663</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="4"/>
+        <v>277.40428270012541</v>
+      </c>
+      <c r="F24">
         <f t="shared" si="5"/>
-        <v>4761.0596707818931</v>
-      </c>
-    </row>
-    <row r="24" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="F24">
+        <v>333764.02249175153</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="6"/>
+        <v>148088.00000000003</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B25">
         <f t="shared" si="4"/>
-        <v>10730.581998834603</v>
-      </c>
-      <c r="G24">
+        <v>1664.4481753776663</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="4"/>
+        <v>1387.0326530890841</v>
+      </c>
+      <c r="F25">
         <f t="shared" si="5"/>
-        <v>4761.0596707818931</v>
-      </c>
-    </row>
-    <row r="25" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="F25">
+        <v>471353.99516706169</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="6"/>
+        <v>148088.00000000003</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B26">
         <f t="shared" si="4"/>
-        <v>15154.127931039791</v>
-      </c>
-      <c r="G25">
+        <v>1664.4481753776663</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="4"/>
+        <v>1109.6283703889585</v>
+      </c>
+      <c r="F26">
         <f t="shared" si="5"/>
-        <v>4761.0596707818931</v>
-      </c>
-    </row>
-    <row r="26" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="F26">
-        <f t="shared" si="4"/>
-        <v>5009.260949016345</v>
+        <v>155808.05255820439</v>
       </c>
       <c r="G26">
+        <f t="shared" si="6"/>
+        <v>148088.00000000003</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="F27">
         <f t="shared" si="5"/>
-        <v>4761.0596707818931</v>
-      </c>
-    </row>
-    <row r="27" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="F27">
-        <f t="shared" si="4"/>
-        <v>8998.1416765727372</v>
+        <v>279878.19870811841</v>
       </c>
       <c r="G27">
+        <f t="shared" si="6"/>
+        <v>148088.00000000003</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="F28">
         <f t="shared" si="5"/>
-        <v>4761.0596707818931</v>
-      </c>
-    </row>
-    <row r="28" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="F28">
-        <f t="shared" si="4"/>
-        <v>7560.7364986884968</v>
+        <v>235169.14805520704</v>
       </c>
       <c r="G28">
-        <f t="shared" si="5"/>
-        <v>4761.0596707818931</v>
-      </c>
-    </row>
-    <row r="31" spans="5:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="6"/>
+        <v>148088.00000000003</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="E31" t="s">
         <v>12</v>
       </c>
       <c r="F31">
         <f>SUM(F17:F28)</f>
-        <v>124724.81202254545</v>
+        <v>3879440.5531492536</v>
       </c>
       <c r="G31">
         <f>SUM(G17:G28)</f>
-        <v>109981.97415750808</v>
+        <v>3420879.3241951307</v>
       </c>
       <c r="H31">
         <f>100*(F31-G31)/F31</f>
-        <v>11.820292711583663</v>
-      </c>
-    </row>
-    <row r="32" spans="5:8" x14ac:dyDescent="0.35">
+        <v>11.820292711583681</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="E32" t="s">
         <v>13</v>
       </c>
       <c r="F32">
         <f>0.05*SUM(K2:K13)</f>
-        <v>6487.2618188794722</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <f>0.05*SUM(L2:L13)</f>
-        <v>13001.567853858884</v>
-      </c>
-      <c r="H32">
-        <f t="shared" ref="H32:H34" si="6">100*(F32-G32)/F32</f>
-        <v>-100.41688183481719</v>
-      </c>
-    </row>
-    <row r="33" spans="5:8" x14ac:dyDescent="0.35">
+        <v>162857.60000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="5:8" x14ac:dyDescent="0.2">
       <c r="E33" t="s">
         <v>14</v>
       </c>
@@ -1143,21 +1256,92 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="5:8" x14ac:dyDescent="0.2">
       <c r="E34" t="s">
         <v>15</v>
       </c>
       <c r="F34">
         <f>SUM(F31:F33)</f>
-        <v>131212.07384142492</v>
+        <v>3879440.5531492536</v>
       </c>
       <c r="G34">
         <f>SUM(G31:G33)</f>
-        <v>122983.54201136697</v>
+        <v>3583736.9241951308</v>
       </c>
       <c r="H34">
-        <f t="shared" si="6"/>
-        <v>6.2711697095821117</v>
+        <f t="shared" ref="H34" si="7">100*(F34-G34)/F34</f>
+        <v>7.6223265933041908</v>
+      </c>
+    </row>
+    <row r="36" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E37" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37">
+        <v>4218</v>
+      </c>
+      <c r="G37">
+        <f>F37*(1-H31/100)</f>
+        <v>3719.4200534254005</v>
+      </c>
+      <c r="H37">
+        <f>F37-G37</f>
+        <v>498.57994657459949</v>
+      </c>
+    </row>
+    <row r="38" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E38" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38">
+        <f>F32*F37/F31</f>
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <f>G32*G37/G31</f>
+        <v>177.07021086902878</v>
+      </c>
+      <c r="H38">
+        <f t="shared" ref="H38:H39" si="8">F38-G38</f>
+        <v>-177.07021086902878</v>
+      </c>
+    </row>
+    <row r="39" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E39" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <f>F39*(1-H33/100)</f>
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E40" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40">
+        <f>SUM(F37:F39)</f>
+        <v>4218</v>
+      </c>
+      <c r="G40">
+        <f>SUM(G37:G39)</f>
+        <v>3896.4902642944294</v>
+      </c>
+      <c r="H40">
+        <f>SUM(H37:H39)</f>
+        <v>321.50973570557073</v>
       </c>
     </row>
   </sheetData>
@@ -1168,14 +1352,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34E3220C-D6E8-CA4D-AC53-28C815E97289}">
-  <dimension ref="A1:L34"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:L40"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="12.6328125" customWidth="1"/>
-    <col min="5" max="5" width="15.6328125" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="41" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
@@ -1213,7 +1397,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>45772</v>
       </c>
@@ -1237,11 +1421,11 @@
         <v>4886.8312757201647</v>
       </c>
       <c r="H2" s="4">
-        <v>5232</v>
+        <v>9513.1687242798362</v>
       </c>
       <c r="I2">
         <f>SUM(G2:H2)</f>
-        <v>10118.831275720164</v>
+        <v>14400</v>
       </c>
       <c r="J2" s="4">
         <v>10314.285714285714</v>
@@ -1252,10 +1436,10 @@
       </c>
       <c r="L2">
         <f>I2-J2</f>
-        <v>-195.45443856554994</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+        <v>4085.7142857142862</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>45802</v>
       </c>
@@ -1296,7 +1480,7 @@
         <v>8920.2674897119323</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>45833</v>
       </c>
@@ -1320,11 +1504,11 @@
         <v>4886.8312757201647</v>
       </c>
       <c r="H4" s="4">
-        <v>3010</v>
+        <v>7000</v>
       </c>
       <c r="I4">
         <f t="shared" si="1"/>
-        <v>7896.8312757201647</v>
+        <v>11886.831275720164</v>
       </c>
       <c r="J4">
         <v>5625.7573205650187</v>
@@ -1337,7 +1521,7 @@
         <v>10904.835390946499</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>45863</v>
       </c>
@@ -1378,7 +1562,7 @@
         <v>14464.763374485594</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>45894</v>
       </c>
@@ -1402,11 +1586,11 @@
         <v>4886.8312757201647</v>
       </c>
       <c r="H6" s="4">
-        <v>6657.9218106995604</v>
+        <v>12000</v>
       </c>
       <c r="I6">
         <f t="shared" si="1"/>
-        <v>11544.753086419725</v>
+        <v>16886.831275720164</v>
       </c>
       <c r="J6">
         <v>6493.9081133646077</v>
@@ -1419,7 +1603,7 @@
         <v>17682.613168724245</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>45925</v>
       </c>
@@ -1443,11 +1627,11 @@
         <v>4886.8312757201647</v>
       </c>
       <c r="H7" s="4">
-        <v>3279.3186831275698</v>
+        <v>7000</v>
       </c>
       <c r="I7">
         <f t="shared" si="1"/>
-        <v>8166.1499588477345</v>
+        <v>11886.831275720164</v>
       </c>
       <c r="J7">
         <v>6071.2326312903115</v>
@@ -1460,7 +1644,7 @@
         <v>19611.623209876507</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>45955</v>
       </c>
@@ -1484,11 +1668,11 @@
         <v>2764.9176954732511</v>
       </c>
       <c r="H8" s="4">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="I8">
         <f t="shared" si="1"/>
-        <v>2764.9176954732511</v>
+        <v>12764.91769547325</v>
       </c>
       <c r="J8">
         <v>6403.8158313631438</v>
@@ -1501,7 +1685,7 @@
         <v>17168.207572016425</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>45986</v>
       </c>
@@ -1542,7 +1726,7 @@
         <v>13698.428765432065</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>46016</v>
       </c>
@@ -1583,7 +1767,7 @@
         <v>9167.6931687242432</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>46047</v>
       </c>
@@ -1624,7 +1808,7 @@
         <v>8302.0810288065477</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>46078</v>
       </c>
@@ -1665,7 +1849,7 @@
         <v>5346.7055144032556</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>46106</v>
       </c>
@@ -1706,7 +1890,7 @@
         <v>2905.7332921810339</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="F16" t="s">
         <v>16</v>
       </c>
@@ -1714,17 +1898,17 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F17">
         <f>B2*D2+C2*E2</f>
         <v>20896.148657136669</v>
       </c>
       <c r="G17">
         <f>B2*G2+C2*H2</f>
-        <v>14854.518288499024</v>
-      </c>
-    </row>
-    <row r="18" spans="5:8" x14ac:dyDescent="0.35">
+        <v>20896.148657136669</v>
+      </c>
+    </row>
+    <row r="18" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F18">
         <f t="shared" ref="F18:F28" si="3">B3*D3+C3*E3</f>
         <v>7724.5691872427979</v>
@@ -1734,17 +1918,17 @@
         <v>7724.5691872427979</v>
       </c>
     </row>
-    <row r="19" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F19">
         <f t="shared" si="3"/>
         <v>15264.614806692658</v>
       </c>
       <c r="G19">
         <f t="shared" si="4"/>
-        <v>12333.886892462639</v>
-      </c>
-    </row>
-    <row r="20" spans="5:8" x14ac:dyDescent="0.35">
+        <v>18164.851892462641</v>
+      </c>
+    </row>
+    <row r="20" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F20">
         <f t="shared" si="3"/>
         <v>11286.624160710418</v>
@@ -1754,37 +1938,37 @@
         <v>14754.93083983106</v>
       </c>
     </row>
-    <row r="21" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F21">
         <f t="shared" si="3"/>
         <v>11286.624160710418</v>
       </c>
       <c r="G21">
         <f t="shared" si="4"/>
-        <v>14421.656662876299</v>
-      </c>
-    </row>
-    <row r="22" spans="5:8" x14ac:dyDescent="0.35">
+        <v>19626.246629304744</v>
+      </c>
+    </row>
+    <row r="22" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F22">
         <f t="shared" si="3"/>
         <v>8373.6103496588712</v>
       </c>
       <c r="G22">
         <f t="shared" si="4"/>
-        <v>9000.0690513786012</v>
-      </c>
-    </row>
-    <row r="23" spans="5:8" x14ac:dyDescent="0.35">
+        <v>10208.38478719948</v>
+      </c>
+    </row>
+    <row r="23" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F23">
         <f t="shared" si="3"/>
         <v>8968.5077519379847</v>
       </c>
       <c r="G23">
         <f t="shared" si="4"/>
-        <v>4761.0596707818931</v>
-      </c>
-    </row>
-    <row r="24" spans="5:8" x14ac:dyDescent="0.35">
+        <v>21980.594554502823</v>
+      </c>
+    </row>
+    <row r="24" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F24">
         <f t="shared" si="3"/>
         <v>10730.581998834603</v>
@@ -1794,7 +1978,7 @@
         <v>4761.0596707818931</v>
       </c>
     </row>
-    <row r="25" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F25">
         <f t="shared" si="3"/>
         <v>15154.127931039791</v>
@@ -1804,7 +1988,7 @@
         <v>4761.0596707818931</v>
       </c>
     </row>
-    <row r="26" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F26">
         <f t="shared" si="3"/>
         <v>5009.260949016345</v>
@@ -1814,7 +1998,7 @@
         <v>4761.0596707818931</v>
       </c>
     </row>
-    <row r="27" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F27">
         <f t="shared" si="3"/>
         <v>8998.1416765727372</v>
@@ -1824,7 +2008,7 @@
         <v>4761.0596707818931</v>
       </c>
     </row>
-    <row r="28" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F28">
         <f t="shared" si="3"/>
         <v>7560.7364986884968</v>
@@ -1834,7 +2018,7 @@
         <v>4761.0596707818931</v>
       </c>
     </row>
-    <row r="31" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="5:8" x14ac:dyDescent="0.2">
       <c r="E31" t="s">
         <v>12</v>
       </c>
@@ -1844,14 +2028,14 @@
       </c>
       <c r="G31">
         <f>SUM(G17:G28)</f>
-        <v>101655.98894698176</v>
+        <v>137161.02490158967</v>
       </c>
       <c r="H31">
         <f>100*(F31-G31)/F31</f>
-        <v>22.549911681123945</v>
-      </c>
-    </row>
-    <row r="32" spans="5:8" x14ac:dyDescent="0.35">
+        <v>-4.500813012365926</v>
+      </c>
+    </row>
+    <row r="32" spans="5:8" x14ac:dyDescent="0.2">
       <c r="E32" t="s">
         <v>13</v>
       </c>
@@ -1861,14 +2045,14 @@
       </c>
       <c r="G32">
         <f>0.05*SUM(L2:L13)</f>
-        <v>6398.8748768371406</v>
+        <v>6612.9333130511313</v>
       </c>
       <c r="H32">
         <f t="shared" ref="H32:H34" si="5">100*(F32-G32)/F32</f>
-        <v>-3.3484303369837409</v>
-      </c>
-    </row>
-    <row r="33" spans="5:8" x14ac:dyDescent="0.35">
+        <v>-6.8056949044134667</v>
+      </c>
+    </row>
+    <row r="33" spans="5:8" x14ac:dyDescent="0.2">
       <c r="E33" t="s">
         <v>14</v>
       </c>
@@ -1879,7 +2063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="5:8" x14ac:dyDescent="0.2">
       <c r="E34" t="s">
         <v>15</v>
       </c>
@@ -1889,11 +2073,82 @@
       </c>
       <c r="G34">
         <f>SUM(G31:G33)</f>
-        <v>108054.8638238189</v>
+        <v>143773.95821464079</v>
       </c>
       <c r="H34">
         <f t="shared" si="5"/>
-        <v>21.383256742769358</v>
+        <v>-4.6046421238897874</v>
+      </c>
+    </row>
+    <row r="36" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E37" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37">
+        <v>4064</v>
+      </c>
+      <c r="G37">
+        <f>F37*(1-H31/100)</f>
+        <v>4246.9130408225519</v>
+      </c>
+      <c r="H37">
+        <f>F37-G37</f>
+        <v>-182.91304082255192</v>
+      </c>
+    </row>
+    <row r="38" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E38" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38">
+        <f>F32*F37/F31</f>
+        <v>191.70894626733826</v>
+      </c>
+      <c r="G38">
+        <f>F38*(1-H32/100)</f>
+        <v>204.75607225475926</v>
+      </c>
+      <c r="H38">
+        <f t="shared" ref="H38:H39" si="6">F38-G38</f>
+        <v>-13.047125987420998</v>
+      </c>
+    </row>
+    <row r="39" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E39" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <f>F39*(1-H33/100)</f>
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E40" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40">
+        <f>SUM(F37:F39)</f>
+        <v>4255.7089462673384</v>
+      </c>
+      <c r="G40">
+        <f>SUM(G37:G39)</f>
+        <v>4451.6691130773115</v>
+      </c>
+      <c r="H40">
+        <f>SUM(H37:H39)</f>
+        <v>-195.96016680997292</v>
       </c>
     </row>
   </sheetData>
@@ -1903,15 +2158,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A487B8A4-70A8-BF44-BD3B-04E3E6FA5695}">
-  <dimension ref="A1:L34"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22649FB6-A099-E345-9FF6-C8AAECD0EDCD}">
+  <dimension ref="A1:L40"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="12.6328125" customWidth="1"/>
-    <col min="5" max="5" width="15.6328125" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="41" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
@@ -1949,7 +2204,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>45772</v>
       </c>
@@ -1973,11 +2228,11 @@
         <v>4886.8312757201647</v>
       </c>
       <c r="H2" s="4">
-        <v>5232</v>
+        <v>6232</v>
       </c>
       <c r="I2">
         <f>SUM(G2:H2)</f>
-        <v>10118.831275720164</v>
+        <v>11118.831275720164</v>
       </c>
       <c r="J2" s="4">
         <v>10314.285714285714</v>
@@ -1987,10 +2242,11 @@
         <v>4085.7142857142862</v>
       </c>
       <c r="L2">
-        <v>2113.1687242798344</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+        <f>I2-J2</f>
+        <v>804.54556143445006</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>45802</v>
       </c>
@@ -2004,34 +2260,34 @@
         <v>4886.8312757201647</v>
       </c>
       <c r="E3" s="2">
-        <v>2570.3115814226921</v>
+        <v>192.90123456790116</v>
       </c>
       <c r="F3">
         <f t="shared" ref="F3:F13" si="0">SUM(D3:E3)</f>
-        <v>7457.1428571428569</v>
+        <v>5079.7325102880659</v>
       </c>
       <c r="G3" s="2">
         <v>4886.8312757201647</v>
       </c>
       <c r="H3" s="4">
-        <v>3032</v>
+        <v>7000</v>
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I13" si="1">SUM(G3:H3)</f>
-        <v>7918.8312757201647</v>
-      </c>
-      <c r="J3" s="4">
-        <v>12000</v>
+        <v>11886.831275720164</v>
+      </c>
+      <c r="J3">
+        <v>5907.1382972953343</v>
       </c>
       <c r="K3">
         <f>K2+F3-J3</f>
-        <v>-457.14285714285688</v>
+        <v>3258.3084987070179</v>
       </c>
       <c r="L3">
         <v>8920.2674897119323</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>45833</v>
       </c>
@@ -2066,13 +2322,13 @@
       </c>
       <c r="K4">
         <f t="shared" ref="K4:K13" si="2">K3+F4-J4</f>
-        <v>3819.3631967777219</v>
+        <v>7534.8145526275966</v>
       </c>
       <c r="L4">
         <v>10904.835390946499</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>45863</v>
       </c>
@@ -2107,13 +2363,13 @@
       </c>
       <c r="K5">
         <f t="shared" si="2"/>
-        <v>5712.2838730610183</v>
+        <v>9427.7352289108931</v>
       </c>
       <c r="L5">
         <v>14464.763374485594</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>45894</v>
       </c>
@@ -2137,24 +2393,24 @@
         <v>4886.8312757201647</v>
       </c>
       <c r="H6" s="4">
-        <v>8676</v>
+        <v>6657.9218106995604</v>
       </c>
       <c r="I6">
         <f t="shared" si="1"/>
-        <v>13562.831275720164</v>
+        <v>11544.753086419725</v>
       </c>
       <c r="J6">
         <v>6493.9081133646077</v>
       </c>
       <c r="K6">
         <f t="shared" si="2"/>
-        <v>7545.2790518774809</v>
+        <v>11260.730407727355</v>
       </c>
       <c r="L6">
         <v>17682.613168724245</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>45925</v>
       </c>
@@ -2189,13 +2445,13 @@
       </c>
       <c r="K7">
         <f t="shared" si="2"/>
-        <v>7711.1863382826432</v>
+        <v>11426.637694132516</v>
       </c>
       <c r="L7">
         <v>19611.623209876507</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>45955</v>
       </c>
@@ -2219,24 +2475,24 @@
         <v>2764.9176954732511</v>
       </c>
       <c r="H8" s="4">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="I8">
         <f t="shared" si="1"/>
-        <v>2764.9176954732511</v>
+        <v>12764.91769547325</v>
       </c>
       <c r="J8">
         <v>6403.8158313631438</v>
       </c>
       <c r="K8">
         <f t="shared" si="2"/>
-        <v>6515.7038402528333</v>
+        <v>10231.155196102707</v>
       </c>
       <c r="L8">
         <v>17168.207572016425</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>45986</v>
       </c>
@@ -2271,13 +2527,13 @@
       </c>
       <c r="K9">
         <f t="shared" si="2"/>
-        <v>6726.3588690479655</v>
+        <v>10441.810224897839</v>
       </c>
       <c r="L9">
         <v>13698.428765432065</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>46016</v>
       </c>
@@ -2312,13 +2568,13 @@
       </c>
       <c r="K10">
         <f t="shared" si="2"/>
-        <v>9544.65700306088</v>
+        <v>13260.108358910755</v>
       </c>
       <c r="L10">
         <v>9167.6931687242432</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>46047</v>
       </c>
@@ -2353,13 +2609,13 @@
       </c>
       <c r="K11">
         <f t="shared" si="2"/>
-        <v>8893.4654216889357</v>
+        <v>12608.916777538809</v>
       </c>
       <c r="L11">
         <v>8302.0810288065477</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>46078</v>
       </c>
@@ -2394,13 +2650,13 @@
       </c>
       <c r="K12">
         <f t="shared" si="2"/>
-        <v>10741.386175884778</v>
+        <v>14456.837531734651</v>
       </c>
       <c r="L12">
         <v>5346.7055144032556</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>46106</v>
       </c>
@@ -2435,13 +2691,13 @@
       </c>
       <c r="K13">
         <f t="shared" si="2"/>
-        <v>12122.879323733307</v>
+        <v>15838.33067958318</v>
       </c>
       <c r="L13">
         <v>2905.7332921810339</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="F16" t="s">
         <v>16</v>
       </c>
@@ -2449,17 +2705,17 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F17">
         <f>B2*D2+C2*E2</f>
         <v>20896.148657136669</v>
       </c>
       <c r="G17">
         <f>B2*G2+C2*H2</f>
-        <v>14854.518288499024</v>
-      </c>
-    </row>
-    <row r="18" spans="5:8" x14ac:dyDescent="0.35">
+        <v>16265.728814814815</v>
+      </c>
+    </row>
+    <row r="18" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F18">
         <f t="shared" ref="F18:F28" si="3">B3*D3+C3*E3</f>
         <v>7724.5691872427979</v>
@@ -2469,7 +2725,7 @@
         <v>7724.5691872427979</v>
       </c>
     </row>
-    <row r="19" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F19">
         <f t="shared" si="3"/>
         <v>15264.614806692658</v>
@@ -2479,7 +2735,7 @@
         <v>18164.851892462641</v>
       </c>
     </row>
-    <row r="20" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F20">
         <f t="shared" si="3"/>
         <v>11286.624160710418</v>
@@ -2489,17 +2745,17 @@
         <v>14754.93083983106</v>
       </c>
     </row>
-    <row r="21" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F21">
         <f t="shared" si="3"/>
         <v>11286.624160710418</v>
       </c>
       <c r="G21">
         <f t="shared" si="4"/>
-        <v>16387.795892462636</v>
-      </c>
-    </row>
-    <row r="22" spans="5:8" x14ac:dyDescent="0.35">
+        <v>14421.656662876299</v>
+      </c>
+    </row>
+    <row r="22" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F22">
         <f t="shared" si="3"/>
         <v>8373.6103496588712</v>
@@ -2509,17 +2765,17 @@
         <v>9000.0690513786012</v>
       </c>
     </row>
-    <row r="23" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F23">
         <f t="shared" si="3"/>
         <v>8968.5077519379847</v>
       </c>
       <c r="G23">
         <f t="shared" si="4"/>
-        <v>4761.0596707818931</v>
-      </c>
-    </row>
-    <row r="24" spans="5:8" x14ac:dyDescent="0.35">
+        <v>21980.594554502823</v>
+      </c>
+    </row>
+    <row r="24" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F24">
         <f t="shared" si="3"/>
         <v>10730.581998834603</v>
@@ -2529,7 +2785,7 @@
         <v>4761.0596707818931</v>
       </c>
     </row>
-    <row r="25" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F25">
         <f t="shared" si="3"/>
         <v>15154.127931039791</v>
@@ -2539,7 +2795,7 @@
         <v>4761.0596707818931</v>
       </c>
     </row>
-    <row r="26" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F26">
         <f t="shared" si="3"/>
         <v>5009.260949016345</v>
@@ -2549,7 +2805,7 @@
         <v>4761.0596707818931</v>
       </c>
     </row>
-    <row r="27" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F27">
         <f t="shared" si="3"/>
         <v>8998.1416765727372</v>
@@ -2559,7 +2815,7 @@
         <v>4761.0596707818931</v>
       </c>
     </row>
-    <row r="28" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F28">
         <f t="shared" si="3"/>
         <v>7560.7364986884968</v>
@@ -2569,7 +2825,7 @@
         <v>4761.0596707818931</v>
       </c>
     </row>
-    <row r="31" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="5:8" x14ac:dyDescent="0.2">
       <c r="E31" t="s">
         <v>12</v>
       </c>
@@ -2579,31 +2835,31 @@
       </c>
       <c r="G31">
         <f>SUM(G17:G28)</f>
-        <v>109453.0931765681</v>
+        <v>126117.69935701849</v>
       </c>
       <c r="H31">
         <f>100*(F31-G31)/F31</f>
-        <v>16.609421430934173</v>
-      </c>
-    </row>
-    <row r="32" spans="5:8" x14ac:dyDescent="0.35">
+        <v>3.9129218558002732</v>
+      </c>
+    </row>
+    <row r="32" spans="5:8" x14ac:dyDescent="0.2">
       <c r="E32" t="s">
         <v>13</v>
       </c>
       <c r="F32">
         <f>0.05*SUM(K2:K13)</f>
-        <v>4148.0567261119495</v>
+        <v>6191.5549718293805</v>
       </c>
       <c r="G32">
         <f>0.05*SUM(L2:L13)</f>
-        <v>6514.3060349794096</v>
+        <v>6448.8748768371406</v>
       </c>
       <c r="H32">
         <f t="shared" ref="H32:H34" si="5">100*(F32-G32)/F32</f>
-        <v>-57.044767347851327</v>
-      </c>
-    </row>
-    <row r="33" spans="5:8" x14ac:dyDescent="0.35">
+        <v>-4.1559819169582752</v>
+      </c>
+    </row>
+    <row r="33" spans="5:8" x14ac:dyDescent="0.2">
       <c r="E33" t="s">
         <v>14</v>
       </c>
@@ -2614,21 +2870,92 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="5:8" x14ac:dyDescent="0.2">
       <c r="E34" t="s">
         <v>15</v>
       </c>
       <c r="F34">
         <f>SUM(F31:F33)</f>
-        <v>135401.60485435373</v>
+        <v>137445.10310007117</v>
       </c>
       <c r="G34">
         <f>SUM(G31:G33)</f>
-        <v>115967.39921154751</v>
+        <v>132566.57423385562</v>
       </c>
       <c r="H34">
         <f t="shared" si="5"/>
-        <v>14.353009821198828</v>
+        <v>3.5494381074192121</v>
+      </c>
+    </row>
+    <row r="36" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E37" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37">
+        <v>4064</v>
+      </c>
+      <c r="G37">
+        <f>F37*(1-H31/100)</f>
+        <v>3904.9788557802767</v>
+      </c>
+      <c r="H37">
+        <f>F37-G37</f>
+        <v>159.02114421972328</v>
+      </c>
+    </row>
+    <row r="38" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E38" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38">
+        <f>F32*F37/F31</f>
+        <v>191.70894626733826</v>
+      </c>
+      <c r="G38">
+        <f>F38*(1-H32/100)</f>
+        <v>199.6763354074001</v>
+      </c>
+      <c r="H38">
+        <f t="shared" ref="H38:H39" si="6">F38-G38</f>
+        <v>-7.9673891400618402</v>
+      </c>
+    </row>
+    <row r="39" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E39" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <f>F39*(1-H33/100)</f>
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E40" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40">
+        <f>SUM(F37:F39)</f>
+        <v>4255.7089462673384</v>
+      </c>
+      <c r="G40">
+        <f>SUM(G37:G39)</f>
+        <v>4104.6551911876768</v>
+      </c>
+      <c r="H40">
+        <f>SUM(H37:H39)</f>
+        <v>151.05375507966144</v>
       </c>
     </row>
   </sheetData>
@@ -2638,15 +2965,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7E44A41-3F86-B94E-AB4B-AA39DD02AB15}">
-  <dimension ref="A1:L37"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A487B8A4-70A8-BF44-BD3B-04E3E6FA5695}">
+  <dimension ref="A1:L40"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="12.6328125" customWidth="1"/>
-    <col min="5" max="5" width="15.6328125" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="41" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
@@ -2684,7 +3011,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>45772</v>
       </c>
@@ -2697,34 +3024,35 @@
       <c r="D2" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="E2" s="5">
-        <v>2483.1669423159556</v>
+      <c r="E2" s="2">
+        <v>9513.1687242798362</v>
       </c>
       <c r="F2">
         <f>SUM(D2:E2)</f>
-        <v>7369.9982180361203</v>
+        <v>14400</v>
       </c>
       <c r="G2" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="H2" s="5">
-        <v>2483.1669423159556</v>
+      <c r="H2" s="4">
+        <v>9513.1687242798362</v>
       </c>
       <c r="I2">
         <f>SUM(G2:H2)</f>
-        <v>7369.9982180361203</v>
-      </c>
-      <c r="J2">
-        <v>5195.1035206425595</v>
+        <v>14400</v>
+      </c>
+      <c r="J2" s="4">
+        <v>10314.285714285714</v>
       </c>
       <c r="K2">
-        <v>4271.1183717419499</v>
+        <f>F2-J2</f>
+        <v>4085.7142857142862</v>
       </c>
       <c r="L2">
-        <v>4271.1183717419508</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+        <v>2113.1687242798344</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>45802</v>
       </c>
@@ -2732,39 +3060,40 @@
         <v>1.5806907894736841</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1.4112105263157895</v>
       </c>
       <c r="D3" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="E3" s="5">
-        <v>0</v>
+      <c r="E3" s="2">
+        <v>2570.3115814226921</v>
       </c>
       <c r="F3">
         <f t="shared" ref="F3:F13" si="0">SUM(D3:E3)</f>
-        <v>4886.8312757201647</v>
+        <v>7457.1428571428569</v>
       </c>
       <c r="G3" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="H3" s="5">
-        <v>0</v>
+      <c r="H3" s="4">
+        <v>2570.3115814226921</v>
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I13" si="1">SUM(G3:H3)</f>
-        <v>4886.8312757201647</v>
-      </c>
-      <c r="J3">
-        <v>5907.1382972953343</v>
+        <v>7457.1428571428569</v>
+      </c>
+      <c r="J3" s="4">
+        <v>12000</v>
       </c>
       <c r="K3">
-        <v>1654.4669661241915</v>
+        <f>K2+F3-J3+1500</f>
+        <v>1042.8571428571431</v>
       </c>
       <c r="L3">
-        <v>1654.4669661241915</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+        <v>8920.2674897119323</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>45833</v>
       </c>
@@ -2777,34 +3106,35 @@
       <c r="D4" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="E4" s="5">
-        <v>2545.222790928924</v>
+      <c r="E4" s="2">
+        <v>5015.4320987654328</v>
       </c>
       <c r="F4">
         <f t="shared" si="0"/>
-        <v>7432.0540666490888</v>
+        <v>9902.2633744855975</v>
       </c>
       <c r="G4" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="H4" s="5">
-        <v>2545.222790928924</v>
+      <c r="H4" s="4">
+        <v>7000</v>
       </c>
       <c r="I4">
         <f t="shared" si="1"/>
-        <v>7432.0540666490888</v>
+        <v>11886.831275720164</v>
       </c>
       <c r="J4">
         <v>5625.7573205650187</v>
       </c>
       <c r="K4">
-        <v>3912.337898729279</v>
+        <f t="shared" ref="K4:K13" si="2">K3+F4-J4</f>
+        <v>5319.3631967777219</v>
       </c>
       <c r="L4">
-        <v>3912.337898729279</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+        <v>10904.835390946499</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>45863</v>
       </c>
@@ -2817,34 +3147,35 @@
       <c r="D5" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="E5" s="5">
-        <v>1371.7405698790662</v>
+      <c r="E5" s="2">
+        <v>3440.0720164609056</v>
       </c>
       <c r="F5">
         <f t="shared" si="0"/>
-        <v>6258.571845599231</v>
+        <v>8326.9032921810704</v>
       </c>
       <c r="G5" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="H5">
-        <v>6307.6131687242596</v>
+      <c r="H5" s="4">
+        <v>7000</v>
       </c>
       <c r="I5">
         <f t="shared" si="1"/>
-        <v>11194.444444444423</v>
+        <v>11886.831275720164</v>
       </c>
       <c r="J5">
         <v>6433.9826158977739</v>
       </c>
       <c r="K5">
-        <v>3693.0744358561019</v>
+        <f t="shared" si="2"/>
+        <v>7212.2838730610183</v>
       </c>
       <c r="L5">
-        <v>9862.9151844125918</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+        <v>14464.763374485594</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>45894</v>
       </c>
@@ -2857,34 +3188,35 @@
       <c r="D6" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="E6" s="5">
-        <v>1371.7405698790662</v>
+      <c r="E6" s="2">
+        <v>3440.0720164609056</v>
       </c>
       <c r="F6">
         <f t="shared" si="0"/>
-        <v>6258.571845599231</v>
+        <v>8326.9032921810704</v>
       </c>
       <c r="G6" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="H6">
-        <v>7000</v>
+      <c r="H6" s="4">
+        <v>8676</v>
       </c>
       <c r="I6">
         <f t="shared" si="1"/>
-        <v>11886.831275720164</v>
+        <v>13562.831275720164</v>
       </c>
       <c r="J6">
         <v>6493.9081133646077</v>
       </c>
       <c r="K6">
-        <v>3398.9041011493814</v>
+        <f t="shared" si="2"/>
+        <v>9045.2790518774818</v>
       </c>
       <c r="L6">
-        <v>16604.069137357037</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+        <v>17682.613168724245</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>45925</v>
       </c>
@@ -2897,34 +3229,35 @@
       <c r="D7" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="E7" s="5">
-        <v>0</v>
+      <c r="E7" s="2">
+        <v>1350.308641975309</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>
-        <v>4886.8312757201647</v>
+        <v>6237.1399176954737</v>
       </c>
       <c r="G7" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="H7">
-        <v>0</v>
+      <c r="H7" s="4">
+        <v>5279.3186831275698</v>
       </c>
       <c r="I7">
         <f t="shared" si="1"/>
-        <v>4886.8312757201647</v>
+        <v>10166.149958847735</v>
       </c>
       <c r="J7">
         <v>6071.2326312903115</v>
       </c>
       <c r="K7">
-        <v>1783.3609890933087</v>
+        <f t="shared" si="2"/>
+        <v>9211.1863382826432</v>
       </c>
       <c r="L7">
-        <v>15123.567442894353</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+        <v>19611.623209876507</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>45955</v>
       </c>
@@ -2937,34 +3270,35 @@
       <c r="D8" s="2">
         <v>2764.9176954732511</v>
       </c>
-      <c r="E8" s="5">
-        <v>4045.6197993210399</v>
+      <c r="E8" s="2">
+        <v>2443.4156378600819</v>
       </c>
       <c r="F8">
         <f t="shared" si="0"/>
-        <v>6810.537494794291</v>
+        <v>5208.333333333333</v>
       </c>
       <c r="G8" s="2">
         <v>2764.9176954732511</v>
       </c>
-      <c r="H8">
-        <v>0</v>
+      <c r="H8" s="4">
+        <v>7000</v>
       </c>
       <c r="I8">
         <f t="shared" si="1"/>
-        <v>2764.9176954732511</v>
+        <v>9764.9176954732502</v>
       </c>
       <c r="J8">
         <v>6403.8158313631438</v>
       </c>
       <c r="K8">
-        <v>2291.7630683822417</v>
+        <f t="shared" si="2"/>
+        <v>8015.7038402528333</v>
       </c>
       <c r="L8">
-        <v>10574.94477303199</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>17168.207572016425</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>45986</v>
       </c>
@@ -2977,34 +3311,35 @@
       <c r="D9" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="E9" s="5">
-        <v>2402.5977708842929</v>
+      <c r="E9" s="2">
+        <v>3469.7788065843624</v>
       </c>
       <c r="F9">
         <f t="shared" si="0"/>
-        <v>5169.9588819954042</v>
+        <v>6237.1399176954737</v>
       </c>
       <c r="G9" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="H9">
-        <v>585.00395061726795</v>
+      <c r="H9" s="4">
+        <v>0</v>
       </c>
       <c r="I9">
         <f t="shared" si="1"/>
-        <v>3352.3650617283793</v>
+        <v>2767.3611111111113</v>
       </c>
       <c r="J9">
         <v>6026.4848889003415</v>
       </c>
       <c r="K9">
-        <v>1221.1055597510699</v>
+        <f t="shared" si="2"/>
+        <v>8226.3588690479664</v>
       </c>
       <c r="L9">
-        <v>7232.2949890670352</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+        <v>13698.428765432065</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>46016</v>
       </c>
@@ -3017,17 +3352,17 @@
       <c r="D10" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="E10" s="5">
-        <v>1957.8353942526392</v>
+      <c r="E10" s="2">
+        <v>4530.7355967078192</v>
       </c>
       <c r="F10">
         <f t="shared" si="0"/>
-        <v>4725.1965053637505</v>
+        <v>7298.0967078189306</v>
       </c>
       <c r="G10" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="4">
         <v>0</v>
       </c>
       <c r="I10">
@@ -3038,13 +3373,14 @@
         <v>4479.7985738060161</v>
       </c>
       <c r="K10">
-        <v>1527.8529741982381</v>
+        <f t="shared" si="2"/>
+        <v>11044.657003060882</v>
       </c>
       <c r="L10">
-        <v>5091.7481606984038</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+        <v>9167.6931687242432</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>46047</v>
       </c>
@@ -3057,17 +3393,17 @@
       <c r="D11" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="E11" s="5">
-        <v>384.25882680588074</v>
+      <c r="E11" s="2">
+        <v>865.61213991769546</v>
       </c>
       <c r="F11">
         <f t="shared" si="0"/>
-        <v>3151.6199379169921</v>
+        <v>3632.9732510288068</v>
       </c>
       <c r="G11" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="4">
         <v>0</v>
       </c>
       <c r="I11">
@@ -3078,13 +3414,14 @@
         <v>4284.164832400751</v>
       </c>
       <c r="K11">
-        <v>112.17185609353919</v>
+        <f t="shared" si="2"/>
+        <v>10393.465421688938</v>
       </c>
       <c r="L11">
-        <v>3195.7435090863532</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+        <v>8302.0810288065477</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>46078</v>
       </c>
@@ -3097,17 +3434,17 @@
       <c r="D12" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="E12" s="5">
-        <v>1188.9143226231608</v>
+      <c r="E12" s="2">
+        <v>2955.3755144032921</v>
       </c>
       <c r="F12">
         <f t="shared" si="0"/>
-        <v>3956.2754337342722</v>
+        <v>5722.7366255144034</v>
       </c>
       <c r="G12" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="4">
         <v>0</v>
       </c>
       <c r="I12">
@@ -3118,13 +3455,14 @@
         <v>3874.8158713185621</v>
       </c>
       <c r="K12">
-        <v>213.99630911317672</v>
+        <f t="shared" si="2"/>
+        <v>12241.386175884778</v>
       </c>
       <c r="L12">
-        <v>1811.4250588270399</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+        <v>5346.7055144032556</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>46106</v>
       </c>
@@ -3137,17 +3475,17 @@
       <c r="D13" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="E13" s="5">
-        <v>1166.5803075057843</v>
+      <c r="E13" s="2">
+        <v>2440.9722222222217</v>
       </c>
       <c r="F13">
         <f t="shared" si="0"/>
-        <v>3933.9414186168956</v>
+        <v>5208.333333333333</v>
       </c>
       <c r="G13" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="4">
         <v>0</v>
       </c>
       <c r="I13">
@@ -3158,19 +3496,14 @@
         <v>3826.840185484803</v>
       </c>
       <c r="K13">
-        <v>347.87285052829304</v>
+        <f t="shared" si="2"/>
+        <v>13622.879323733307</v>
       </c>
       <c r="L13">
-        <v>487.07621585992513</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="E14" s="5">
-        <f>SUM(E2:E13)</f>
-        <v>18917.677294395813</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+        <v>2905.7332921810339</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="F16" t="s">
         <v>16</v>
       </c>
@@ -3178,161 +3511,161 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F17">
-        <v>232380</v>
+        <f>B2*D2+C2*E2</f>
+        <v>20896.148657136669</v>
       </c>
       <c r="G17">
-        <v>108996.8553735357</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.35">
+        <f>B2*G2+C2*H2</f>
+        <v>20896.148657136669</v>
+      </c>
+    </row>
+    <row r="18" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F18">
-        <v>240264.99999999997</v>
+        <f t="shared" ref="F18:F28" si="3">B3*D3+C3*E3</f>
+        <v>11351.819946857884</v>
       </c>
       <c r="G18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
+        <f t="shared" ref="G18:G28" si="4">B3*G3+C3*H3</f>
+        <v>11351.819946857884</v>
+      </c>
+    </row>
+    <row r="19" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F19">
-        <v>246813</v>
+        <f t="shared" si="3"/>
+        <v>15264.614806692658</v>
       </c>
       <c r="G19">
-        <v>115693.66673321562</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="C20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" t="s">
-        <v>20</v>
-      </c>
+        <f t="shared" si="4"/>
+        <v>18164.851892462641</v>
+      </c>
+    </row>
+    <row r="20" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F20">
-        <v>246813</v>
+        <f t="shared" si="3"/>
+        <v>11286.624160710418</v>
       </c>
       <c r="G20">
-        <v>41568.514657243817</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21">
-        <v>2348425</v>
-      </c>
-      <c r="D21">
-        <v>890831.11158837902</v>
-      </c>
+        <f t="shared" si="4"/>
+        <v>14754.93083983106</v>
+      </c>
+    </row>
+    <row r="21" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F21">
-        <v>246813</v>
+        <f t="shared" si="3"/>
+        <v>11286.624160710418</v>
       </c>
       <c r="G21">
-        <v>41568.514657243817</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B22" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22">
-        <v>2348425</v>
-      </c>
-      <c r="D22">
-        <v>659262.465350062</v>
-      </c>
+        <f t="shared" si="4"/>
+        <v>16387.795892462636</v>
+      </c>
+    </row>
+    <row r="22" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F22">
-        <v>246813</v>
+        <f t="shared" si="3"/>
+        <v>8373.6103496588712</v>
       </c>
       <c r="G22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>9649.5822092733379</v>
+      </c>
+    </row>
+    <row r="23" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F23">
-        <v>148088</v>
+        <f t="shared" si="3"/>
+        <v>8968.5077519379847</v>
       </c>
       <c r="G23">
-        <v>216681.9452972213</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>16814.734089386544</v>
+      </c>
+    </row>
+    <row r="24" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F24">
-        <v>148088.00000000003</v>
+        <f t="shared" si="3"/>
+        <v>10730.581998834603</v>
       </c>
       <c r="G24">
-        <v>128568.65599005947</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="25" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F25">
-        <v>148088.00000000003</v>
+        <f t="shared" si="3"/>
+        <v>15154.127931039791</v>
       </c>
       <c r="G25">
-        <v>139690.69560277648</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="26" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F26">
-        <v>148088.00000000003</v>
+        <f t="shared" si="3"/>
+        <v>5009.260949016345</v>
       </c>
       <c r="G26">
-        <v>3427.052604850729</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="27" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F27">
-        <v>148088.00000000003</v>
+        <f t="shared" si="3"/>
+        <v>8998.1416765727372</v>
       </c>
       <c r="G27">
-        <v>53017.714351968039</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="28" spans="5:8" x14ac:dyDescent="0.2">
       <c r="F28">
-        <v>148088.00000000003</v>
+        <f t="shared" si="3"/>
+        <v>7560.7364986884968</v>
       </c>
       <c r="G28">
-        <v>41617.496320264065</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="31" spans="5:8" x14ac:dyDescent="0.2">
       <c r="E31" t="s">
         <v>12</v>
       </c>
       <c r="F31">
-        <f>SUM(C21:D21)</f>
-        <v>3239256.1115883789</v>
+        <f>SUM(F17:F28)</f>
+        <v>134880.79888785689</v>
       </c>
       <c r="G31">
-        <f>SUM(C22:D22)</f>
-        <v>3007687.4653500621</v>
+        <f>SUM(G17:G28)</f>
+        <v>131825.16188132024</v>
       </c>
       <c r="H31">
         <f>100*(F31-G31)/F31</f>
-        <v>7.1488217745390443</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.35">
+        <v>2.2654351336376495</v>
+      </c>
+    </row>
+    <row r="32" spans="5:8" x14ac:dyDescent="0.2">
       <c r="E32" t="s">
         <v>13</v>
       </c>
       <c r="F32">
-        <f>SUM(K2:K13)</f>
-        <v>24428.025380760773</v>
+        <f>0.05*SUM(K2:K13)</f>
+        <v>4973.0567261119504</v>
       </c>
       <c r="G32">
-        <f>SUM(L2:L13)</f>
-        <v>79821.707707830152</v>
+        <f>0.05*SUM(L2:L13)</f>
+        <v>6514.3060349794096</v>
       </c>
       <c r="H32">
-        <f t="shared" ref="H32:H34" si="2">100*(F32-G32)/F32</f>
-        <v>-226.76283270401706</v>
-      </c>
-    </row>
-    <row r="33" spans="5:8" x14ac:dyDescent="0.35">
+        <f t="shared" ref="H32:H34" si="5">100*(F32-G32)/F32</f>
+        <v>-30.991991319440331</v>
+      </c>
+    </row>
+    <row r="33" spans="5:8" x14ac:dyDescent="0.2">
       <c r="E33" t="s">
         <v>14</v>
       </c>
@@ -3343,26 +3676,92 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="5:8" x14ac:dyDescent="0.2">
       <c r="E34" t="s">
         <v>15</v>
       </c>
       <c r="F34">
         <f>SUM(F31:F33)</f>
-        <v>3263684.1369691398</v>
+        <v>139853.85561396883</v>
       </c>
       <c r="G34">
         <f>SUM(G31:G33)</f>
-        <v>3087509.1730578924</v>
+        <v>138339.46791629965</v>
       </c>
       <c r="H34">
-        <f t="shared" si="2"/>
-        <v>5.3980396545008329</v>
-      </c>
-    </row>
-    <row r="37" spans="5:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v>1.0828358582042004</v>
+      </c>
+    </row>
+    <row r="36" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E37" t="s">
+        <v>12</v>
+      </c>
       <c r="F37">
-        <v>3276</v>
+        <v>3661</v>
+      </c>
+      <c r="G37">
+        <f>F37*(1-H31/100)</f>
+        <v>3578.0624197575257</v>
+      </c>
+      <c r="H37">
+        <f>F37-G37</f>
+        <v>82.937580242474269</v>
+      </c>
+    </row>
+    <row r="38" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E38" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38">
+        <f>F32*F37/F31</f>
+        <v>134.98111535825831</v>
+      </c>
+      <c r="G38">
+        <f>F38*(1-H32/100)</f>
+        <v>176.81445091297346</v>
+      </c>
+      <c r="H38">
+        <f t="shared" ref="H38:H39" si="6">F38-G38</f>
+        <v>-41.833335554715148</v>
+      </c>
+    </row>
+    <row r="39" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E39" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <f>F39*(1-H33/100)</f>
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E40" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40">
+        <f>SUM(F37:F39)</f>
+        <v>3795.9811153582582</v>
+      </c>
+      <c r="G40">
+        <f>SUM(G37:G39)</f>
+        <v>3754.8768706704991</v>
+      </c>
+      <c r="H40">
+        <f>SUM(H37:H39)</f>
+        <v>41.10424468775912</v>
       </c>
     </row>
   </sheetData>
@@ -3372,15 +3771,15 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42DA7594-E291-8048-9A99-303698ABB733}">
-  <dimension ref="A1:L34"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7E44A41-3F86-B94E-AB4B-AA39DD02AB15}">
+  <dimension ref="A1:L46"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="12.6328125" customWidth="1"/>
-    <col min="5" max="5" width="15.6328125" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="41" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
@@ -3418,7 +3817,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>45772</v>
       </c>
@@ -3431,12 +3830,12 @@
       <c r="D2" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="E2" s="2">
-        <v>9513.1687242798362</v>
+      <c r="E2" s="5">
+        <v>2483.1669423159556</v>
       </c>
       <c r="F2">
         <f>SUM(D2:E2)</f>
-        <v>14400</v>
+        <v>7369.9982180361203</v>
       </c>
       <c r="G2" s="2">
         <v>4886.8312757201647</v>
@@ -3448,17 +3847,17 @@
         <f>SUM(G2:H2)</f>
         <v>14400</v>
       </c>
-      <c r="J2" s="4">
-        <v>10314.285714285714</v>
+      <c r="J2">
+        <v>5195.1035206425595</v>
       </c>
       <c r="K2">
-        <v>5085.7142857142862</v>
+        <v>4271.1183717419499</v>
       </c>
       <c r="L2">
-        <v>2113.1687242798344</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+        <v>4271.1183717419508</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>45802</v>
       </c>
@@ -3471,12 +3870,12 @@
       <c r="D3" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="E3" s="2">
-        <v>2570.3115814226921</v>
+      <c r="E3" s="5">
+        <v>0</v>
       </c>
       <c r="F3">
         <f t="shared" ref="F3:F13" si="0">SUM(D3:E3)</f>
-        <v>7457.1428571428569</v>
+        <v>4886.8312757201647</v>
       </c>
       <c r="G3" s="2">
         <v>4886.8312757201647</v>
@@ -3488,17 +3887,17 @@
         <f t="shared" ref="I3:I13" si="1">SUM(G3:H3)</f>
         <v>7457.1428571428569</v>
       </c>
-      <c r="J3" s="4">
-        <v>12000</v>
+      <c r="J3">
+        <v>5907.1382972953343</v>
       </c>
       <c r="K3">
-        <v>542.85714285714312</v>
+        <v>1654.4669661241915</v>
       </c>
       <c r="L3">
-        <v>8920.2674897119323</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+        <v>1654.4669661241915</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>45833</v>
       </c>
@@ -3511,12 +3910,12 @@
       <c r="D4" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="E4" s="2">
-        <v>9627.4544385655499</v>
+      <c r="E4" s="5">
+        <v>2545.222790928924</v>
       </c>
       <c r="F4">
         <f t="shared" si="0"/>
-        <v>14514.285714285714</v>
+        <v>7432.0540666490888</v>
       </c>
       <c r="G4" s="2">
         <v>4886.8312757201647</v>
@@ -3528,17 +3927,17 @@
         <f t="shared" si="1"/>
         <v>14514.285714285714</v>
       </c>
-      <c r="J4" s="4">
-        <v>9828.5714285714294</v>
+      <c r="J4">
+        <v>5625.7573205650187</v>
       </c>
       <c r="K4">
-        <v>5228.5714285714275</v>
+        <v>3912.337898729279</v>
       </c>
       <c r="L4">
-        <v>10904.835390946499</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+        <v>3912.337898729279</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>45863</v>
       </c>
@@ -3551,34 +3950,34 @@
       <c r="D5" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="E5" s="2">
-        <v>7341.7401528512646</v>
+      <c r="E5" s="5">
+        <v>1371.7405698790662</v>
       </c>
       <c r="F5">
         <f t="shared" si="0"/>
-        <v>12228.571428571429</v>
+        <v>6258.571845599231</v>
       </c>
       <c r="G5" s="2">
         <v>4886.8312757201647</v>
       </c>
       <c r="H5" s="4">
-        <v>7341.7401528512646</v>
+        <v>7000</v>
       </c>
       <c r="I5">
         <f t="shared" si="1"/>
-        <v>12228.571428571429</v>
-      </c>
-      <c r="J5" s="4">
-        <v>12457.142857142857</v>
+        <v>11886.831275720164</v>
+      </c>
+      <c r="J5">
+        <v>6433.9826158977739</v>
       </c>
       <c r="K5">
-        <v>4999.9999999999982</v>
+        <v>3693.0744358561019</v>
       </c>
       <c r="L5">
-        <v>14464.763374485594</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+        <v>9862.9151844125918</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>45894</v>
       </c>
@@ -3591,34 +3990,34 @@
       <c r="D6" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="E6" s="2">
-        <v>7341.7401528512646</v>
+      <c r="E6" s="5">
+        <v>1371.7405698790662</v>
       </c>
       <c r="F6">
         <f t="shared" si="0"/>
-        <v>12228.571428571429</v>
+        <v>6258.571845599231</v>
       </c>
       <c r="G6" s="2">
         <v>4886.8312757201647</v>
       </c>
       <c r="H6" s="4">
-        <v>15000</v>
+        <v>6657.9218106995604</v>
       </c>
       <c r="I6">
         <f t="shared" si="1"/>
-        <v>19886.831275720164</v>
-      </c>
-      <c r="J6" s="4">
-        <v>12657.142857142857</v>
+        <v>11544.753086419725</v>
+      </c>
+      <c r="J6">
+        <v>6493.9081133646077</v>
       </c>
       <c r="K6">
-        <v>4571.4285714285706</v>
+        <v>3398.9041011493814</v>
       </c>
       <c r="L6">
-        <v>17682.613168724245</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+        <v>16604.069137357037</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>45925</v>
       </c>
@@ -3631,34 +4030,34 @@
       <c r="D7" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="E7" s="2">
-        <v>4456.0258671369784</v>
+      <c r="E7" s="5">
+        <v>0</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>
-        <v>9342.8571428571431</v>
+        <v>4886.8312757201647</v>
       </c>
       <c r="G7" s="2">
         <v>4886.8312757201647</v>
       </c>
-      <c r="H7" s="4">
-        <v>15000</v>
+      <c r="H7">
+        <v>0</v>
       </c>
       <c r="I7">
         <f t="shared" si="1"/>
-        <v>19886.831275720164</v>
-      </c>
-      <c r="J7" s="4">
-        <v>12000</v>
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="J7">
+        <v>6071.2326312903115</v>
       </c>
       <c r="K7">
-        <v>1914.2857142857138</v>
+        <v>1783.3609890933087</v>
       </c>
       <c r="L7">
-        <v>19611.623209876507</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+        <v>15123.567442894353</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>45955</v>
       </c>
@@ -3669,36 +4068,36 @@
         <v>1.7219534883720931</v>
       </c>
       <c r="D8" s="2">
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="E8" s="2">
-        <v>10546.924603174602</v>
+        <v>2764.9176954732511</v>
+      </c>
+      <c r="E8" s="5">
+        <v>4045.6197993210399</v>
       </c>
       <c r="F8">
         <f t="shared" si="0"/>
-        <v>13314.285714285714</v>
+        <v>6810.537494794291</v>
       </c>
       <c r="G8" s="2">
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="H8" s="4">
-        <v>15000</v>
+        <v>2764.9176954732511</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
       </c>
       <c r="I8">
         <f t="shared" si="1"/>
-        <v>17767.361111111109</v>
-      </c>
-      <c r="J8" s="4">
-        <v>11714.285714285714</v>
+        <v>2764.9176954732511</v>
+      </c>
+      <c r="J8">
+        <v>6403.8158313631438</v>
       </c>
       <c r="K8">
-        <v>3514.2857142857138</v>
+        <v>2291.7630683822417</v>
       </c>
       <c r="L8">
-        <v>17168.207572016425</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>10574.94477303199</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>45986</v>
       </c>
@@ -3711,34 +4110,34 @@
       <c r="D9" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="E9" s="2">
-        <v>7346.9246031746025</v>
+      <c r="E9" s="5">
+        <v>2402.5977708842929</v>
       </c>
       <c r="F9">
         <f t="shared" si="0"/>
-        <v>10114.285714285714</v>
+        <v>5169.9588819954042</v>
       </c>
       <c r="G9" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="H9" s="4">
-        <v>3088.8718871251899</v>
+      <c r="H9">
+        <v>585.00395061726795</v>
       </c>
       <c r="I9">
         <f t="shared" si="1"/>
-        <v>5856.2329982363008</v>
-      </c>
-      <c r="J9" s="4">
-        <v>9342.8571428571431</v>
+        <v>3352.3650617283793</v>
+      </c>
+      <c r="J9">
+        <v>6026.4848889003415</v>
       </c>
       <c r="K9">
-        <v>4285.7142857142844</v>
+        <v>1221.1055597510699</v>
       </c>
       <c r="L9">
-        <v>13698.428765432065</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+        <v>7232.2949890670352</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>46016</v>
       </c>
@@ -3751,34 +4150,34 @@
       <c r="D10" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="E10" s="2">
-        <v>6461.210317460318</v>
+      <c r="E10" s="5">
+        <v>1957.8353942526392</v>
       </c>
       <c r="F10">
         <f t="shared" si="0"/>
-        <v>9228.5714285714294</v>
+        <v>4725.1965053637505</v>
       </c>
       <c r="G10" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
         <f t="shared" si="1"/>
         <v>2767.3611111111113</v>
       </c>
-      <c r="J10" s="4">
-        <v>9085.7142857142862</v>
+      <c r="J10">
+        <v>4479.7985738060161</v>
       </c>
       <c r="K10">
-        <v>4428.5714285714275</v>
+        <v>1527.8529741982381</v>
       </c>
       <c r="L10">
-        <v>9167.6931687242432</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+        <v>5091.7481606984038</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>46047</v>
       </c>
@@ -3791,34 +4190,34 @@
       <c r="D11" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="E11" s="2">
-        <v>3404.0674603174602</v>
+      <c r="E11" s="5">
+        <v>384.25882680588074</v>
       </c>
       <c r="F11">
         <f t="shared" si="0"/>
-        <v>6171.4285714285716</v>
+        <v>3151.6199379169921</v>
       </c>
       <c r="G11" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
         <f t="shared" si="1"/>
         <v>2767.3611111111113</v>
       </c>
-      <c r="J11" s="4">
-        <v>9028.5714285714294</v>
+      <c r="J11">
+        <v>4284.164832400751</v>
       </c>
       <c r="K11">
-        <v>1571.4285714285706</v>
+        <v>112.17185609353919</v>
       </c>
       <c r="L11">
-        <v>8302.0810288065477</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+        <v>3195.7435090863532</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>46078</v>
       </c>
@@ -3831,34 +4230,34 @@
       <c r="D12" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="E12" s="2">
-        <v>4975.4960317460318</v>
+      <c r="E12" s="5">
+        <v>1188.9143226231608</v>
       </c>
       <c r="F12">
         <f t="shared" si="0"/>
-        <v>7742.8571428571431</v>
+        <v>3956.2754337342722</v>
       </c>
       <c r="G12" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
         <f t="shared" si="1"/>
         <v>2767.3611111111113</v>
       </c>
-      <c r="J12" s="4">
-        <v>7685.7142857142853</v>
+      <c r="J12">
+        <v>3874.8158713185621</v>
       </c>
       <c r="K12">
-        <v>1628.5714285714284</v>
+        <v>213.99630911317672</v>
       </c>
       <c r="L12">
-        <v>5346.7055144032556</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+        <v>1811.4250588270399</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>46106</v>
       </c>
@@ -3871,34 +4270,40 @@
       <c r="D13" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="E13" s="2">
-        <v>4918.353174603174</v>
+      <c r="E13" s="5">
+        <v>1166.5803075057843</v>
       </c>
       <c r="F13">
         <f t="shared" si="0"/>
-        <v>7685.7142857142853</v>
+        <v>3933.9414186168956</v>
       </c>
       <c r="G13" s="2">
         <v>2767.3611111111113</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
         <f t="shared" si="1"/>
         <v>2767.3611111111113</v>
       </c>
-      <c r="J13" s="4">
-        <v>7571.4285714285716</v>
+      <c r="J13">
+        <v>3826.840185484803</v>
       </c>
       <c r="K13">
-        <v>1742.8571428571422</v>
+        <v>347.87285052829304</v>
       </c>
       <c r="L13">
-        <v>2905.7332921810339</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+        <v>487.07621585992513</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="E14" s="5">
+        <f>SUM(E2:E13)</f>
+        <v>18917.677294395813</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="F16" t="s">
         <v>16</v>
       </c>
@@ -3906,161 +4311,161 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F17">
-        <f>B2*D2+C2*E2</f>
-        <v>20896.148657136669</v>
+        <v>232380</v>
       </c>
       <c r="G17">
-        <f>B2*G2+C2*H2</f>
-        <v>20896.148657136669</v>
-      </c>
-    </row>
-    <row r="18" spans="5:8" x14ac:dyDescent="0.35">
+        <v>108996.8553735357</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F18">
-        <f t="shared" ref="F18:F28" si="2">B3*D3+C3*E3</f>
-        <v>7724.5691872427979</v>
+        <v>240264.99999999997</v>
       </c>
       <c r="G18">
-        <f t="shared" ref="G18:G28" si="3">B3*G3+C3*H3</f>
-        <v>7724.5691872427979</v>
-      </c>
-    </row>
-    <row r="19" spans="5:8" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F19">
-        <f t="shared" si="2"/>
-        <v>22004.599980274761</v>
+        <v>246813</v>
       </c>
       <c r="G19">
-        <f t="shared" si="3"/>
-        <v>22004.599980274761</v>
-      </c>
-    </row>
-    <row r="20" spans="5:8" x14ac:dyDescent="0.35">
+        <v>115693.66673321562</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="C20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" t="s">
+        <v>20</v>
+      </c>
       <c r="F20">
-        <f t="shared" si="2"/>
-        <v>15087.875680327363</v>
+        <v>246813</v>
       </c>
       <c r="G20">
-        <f t="shared" si="3"/>
-        <v>15087.875680327363</v>
-      </c>
-    </row>
-    <row r="21" spans="5:8" x14ac:dyDescent="0.35">
+        <v>41568.514657243817</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21">
+        <v>2348425</v>
+      </c>
+      <c r="D21">
+        <v>890831.11158837902</v>
+      </c>
       <c r="F21">
-        <f t="shared" si="2"/>
-        <v>15087.875680327363</v>
+        <v>246813</v>
       </c>
       <c r="G21">
-        <f t="shared" si="3"/>
-        <v>22549.036102988954</v>
-      </c>
-    </row>
-    <row r="22" spans="5:8" x14ac:dyDescent="0.35">
+        <v>41568.514657243817</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22">
+        <v>2348425</v>
+      </c>
+      <c r="D22">
+        <v>659262.465350062</v>
+      </c>
       <c r="F22">
-        <f t="shared" si="2"/>
-        <v>9382.2124508802881</v>
+        <v>246813</v>
       </c>
       <c r="G22">
-        <f t="shared" si="3"/>
-        <v>12806.437418778429</v>
-      </c>
-    </row>
-    <row r="23" spans="5:8" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F23">
-        <f t="shared" si="2"/>
-        <v>22926.580730897007</v>
+        <v>148088</v>
       </c>
       <c r="G23">
-        <f t="shared" si="3"/>
-        <v>30594.569444444445</v>
-      </c>
-    </row>
-    <row r="24" spans="5:8" x14ac:dyDescent="0.35">
+        <v>216681.9452972213</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F24">
-        <f t="shared" si="2"/>
-        <v>17400.951982633287</v>
+        <v>148088.00000000003</v>
       </c>
       <c r="G24">
-        <f t="shared" si="3"/>
-        <v>10075.257124434422</v>
-      </c>
-    </row>
-    <row r="25" spans="5:8" x14ac:dyDescent="0.35">
+        <v>128568.65599005947</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F25">
-        <f t="shared" si="2"/>
-        <v>19582.449804878968</v>
+        <v>148088.00000000003</v>
       </c>
       <c r="G25">
-        <f t="shared" si="3"/>
-        <v>4761.0596707818931</v>
-      </c>
-    </row>
-    <row r="26" spans="5:8" x14ac:dyDescent="0.35">
+        <v>139690.69560277648</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F26">
-        <f t="shared" si="2"/>
-        <v>5737.1248804581701</v>
+        <v>148088.00000000003</v>
       </c>
       <c r="G26">
-        <f t="shared" si="3"/>
-        <v>4761.0596707818931</v>
-      </c>
-    </row>
-    <row r="27" spans="5:8" x14ac:dyDescent="0.35">
+        <v>3427.052604850729</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F27">
-        <f t="shared" si="2"/>
-        <v>11894.361210045459</v>
+        <v>148088.00000000003</v>
       </c>
       <c r="G27">
-        <f t="shared" si="3"/>
-        <v>4761.0596707818931</v>
-      </c>
-    </row>
-    <row r="28" spans="5:8" x14ac:dyDescent="0.35">
+        <v>53017.714351968039</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F28">
-        <f t="shared" si="2"/>
-        <v>10402.172375399885</v>
+        <v>148088.00000000003</v>
       </c>
       <c r="G28">
-        <f t="shared" si="3"/>
-        <v>4761.0596707818931</v>
-      </c>
-    </row>
-    <row r="31" spans="5:8" x14ac:dyDescent="0.35">
+        <v>41617.496320264065</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="E31" t="s">
         <v>12</v>
       </c>
       <c r="F31">
-        <f>SUM(F17:F28)</f>
-        <v>178126.92262050201</v>
+        <f>SUM(C21:D21)</f>
+        <v>3239256.1115883789</v>
       </c>
       <c r="G31">
-        <f>SUM(G17:G28)</f>
-        <v>160782.7322787554</v>
+        <f>SUM(C22:D22)</f>
+        <v>3007687.4653500621</v>
       </c>
       <c r="H31">
         <f>100*(F31-G31)/F31</f>
-        <v>9.7369842169778398</v>
-      </c>
-    </row>
-    <row r="32" spans="5:8" x14ac:dyDescent="0.35">
+        <v>7.1488217745390443</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="E32" t="s">
         <v>13</v>
       </c>
       <c r="F32">
-        <f>0.05*SUM(K2:K13)</f>
-        <v>1975.7142857142856</v>
+        <f>SUM(K2:K13)</f>
+        <v>24428.025380760773</v>
       </c>
       <c r="G32">
-        <f>0.05*SUM(L2:L13)</f>
-        <v>6514.3060349794096</v>
+        <f>SUM(L2:L13)</f>
+        <v>79821.707707830152</v>
       </c>
       <c r="H32">
-        <f t="shared" ref="H32:H34" si="4">100*(F32-G32)/F32</f>
-        <v>-229.71903286229841</v>
-      </c>
-    </row>
-    <row r="33" spans="5:8" x14ac:dyDescent="0.35">
+        <f t="shared" ref="H32:H34" si="2">100*(F32-G32)/F32</f>
+        <v>-226.76283270401706</v>
+      </c>
+    </row>
+    <row r="33" spans="5:8" x14ac:dyDescent="0.2">
       <c r="E33" t="s">
         <v>14</v>
       </c>
@@ -4071,25 +4476,956 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="5:8" x14ac:dyDescent="0.2">
       <c r="E34" t="s">
         <v>15</v>
       </c>
       <c r="F34">
         <f>SUM(F31:F33)</f>
-        <v>180102.6369062163</v>
+        <v>3263684.1369691398</v>
       </c>
       <c r="G34">
         <f>SUM(G31:G33)</f>
-        <v>167297.03831373481</v>
+        <v>3087509.1730578924</v>
       </c>
       <c r="H34">
+        <f t="shared" si="2"/>
+        <v>5.3980396545008329</v>
+      </c>
+    </row>
+    <row r="37" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E37" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37">
+        <f>F31/30.15</f>
+        <v>107438.01365135585</v>
+      </c>
+      <c r="G37">
+        <f>G31/30.15</f>
+        <v>99757.461537315496</v>
+      </c>
+      <c r="H37">
+        <f>100*(F37-G37)/F37</f>
+        <v>7.1488217745390443</v>
+      </c>
+    </row>
+    <row r="38" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E38" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38">
+        <f t="shared" ref="F38:G38" si="3">F32/30.15</f>
+        <v>810.21643053932917</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="3"/>
+        <v>2647.4861594636868</v>
+      </c>
+      <c r="H38">
+        <f t="shared" ref="H38:H40" si="4">100*(F38-G38)/F38</f>
+        <v>-226.76283270401706</v>
+      </c>
+    </row>
+    <row r="39" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E39" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39">
+        <f t="shared" ref="F39:G39" si="5">F33/30.15</f>
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E40" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40">
+        <f t="shared" ref="F40:G40" si="6">F34/32.15</f>
+        <v>101514.28108768709</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="6"/>
+        <v>96034.499939592308</v>
+      </c>
+      <c r="H40">
         <f t="shared" si="4"/>
-        <v>7.1101671871409993</v>
+        <v>5.3980396545008302</v>
+      </c>
+    </row>
+    <row r="42" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E42" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43">
+        <v>3661</v>
+      </c>
+      <c r="G43">
+        <f>F43*(1-H37/100)</f>
+        <v>3399.2816348341257</v>
+      </c>
+      <c r="H43">
+        <f>F43-G43</f>
+        <v>261.71836516587427</v>
+      </c>
+    </row>
+    <row r="44" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E44" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44">
+        <f>F38*F43/F37</f>
+        <v>27.60849955612569</v>
+      </c>
+      <c r="G44">
+        <f>F44*(1-H38/100)</f>
+        <v>90.214315216672276</v>
+      </c>
+      <c r="H44">
+        <f t="shared" ref="H44:H45" si="7">F44-G44</f>
+        <v>-62.605815660546583</v>
+      </c>
+    </row>
+    <row r="45" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E45" t="s">
+        <v>14</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <f>F45*(1-H39/100)</f>
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E46" t="s">
+        <v>15</v>
+      </c>
+      <c r="F46">
+        <f>SUM(F43:F45)</f>
+        <v>3688.6084995561255</v>
+      </c>
+      <c r="G46">
+        <f>SUM(G43:G45)</f>
+        <v>3489.495950050798</v>
+      </c>
+      <c r="H46">
+        <f>SUM(H43:H45)</f>
+        <v>199.11254950532771</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42DA7594-E291-8048-9A99-303698ABB733}">
+  <dimension ref="A1:L39"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>45772</v>
+      </c>
+      <c r="B2">
+        <v>1.5288157894736842</v>
+      </c>
+      <c r="C2">
+        <v>1.4112105263157895</v>
+      </c>
+      <c r="D2" s="2">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="E2" s="2">
+        <v>9513.1687242798362</v>
+      </c>
+      <c r="F2">
+        <f>SUM(D2:E2)</f>
+        <v>14400</v>
+      </c>
+      <c r="G2" s="2">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="H2" s="4">
+        <v>9513.1687242798362</v>
+      </c>
+      <c r="I2">
+        <f>SUM(G2:H2)</f>
+        <v>14400</v>
+      </c>
+      <c r="J2" s="4">
+        <v>10314.285714285714</v>
+      </c>
+      <c r="K2">
+        <v>5085.7142857142862</v>
+      </c>
+      <c r="L2">
+        <v>2113.1687242798344</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>45802</v>
+      </c>
+      <c r="B3">
+        <v>1.5806907894736841</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="E3" s="2">
+        <v>2570.3115814226921</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F13" si="0">SUM(D3:E3)</f>
+        <v>7457.1428571428569</v>
+      </c>
+      <c r="G3" s="2">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="H3" s="4">
+        <v>2570.3115814226921</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I13" si="1">SUM(G3:H3)</f>
+        <v>7457.1428571428569</v>
+      </c>
+      <c r="J3" s="4">
+        <v>12000</v>
+      </c>
+      <c r="K3">
+        <v>542.85714285714312</v>
+      </c>
+      <c r="L3">
+        <v>8920.2674897119323</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>45833</v>
+      </c>
+      <c r="B4">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="C4">
+        <v>1.4613947368421052</v>
+      </c>
+      <c r="D4" s="2">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="E4" s="2">
+        <v>9627.4544385655499</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>14514.285714285714</v>
+      </c>
+      <c r="G4" s="2">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="H4" s="4">
+        <v>9627.4544385655499</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="1"/>
+        <v>14514.285714285714</v>
+      </c>
+      <c r="J4" s="4">
+        <v>9828.5714285714294</v>
+      </c>
+      <c r="K4">
+        <v>5228.5714285714275</v>
+      </c>
+      <c r="L4">
+        <v>10904.835390946499</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>45863</v>
+      </c>
+      <c r="B5">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="C5">
+        <v>0.97426315789473683</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="E5" s="2">
+        <v>7341.7401528512646</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>12228.571428571429</v>
+      </c>
+      <c r="G5" s="2">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="H5" s="4">
+        <v>7341.7401528512646</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="1"/>
+        <v>12228.571428571429</v>
+      </c>
+      <c r="J5" s="4">
+        <v>12457.142857142857</v>
+      </c>
+      <c r="K5">
+        <v>4999.9999999999982</v>
+      </c>
+      <c r="L5">
+        <v>14464.763374485594</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>45894</v>
+      </c>
+      <c r="B6">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="C6">
+        <v>0.97426315789473683</v>
+      </c>
+      <c r="D6" s="2">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="E6" s="2">
+        <v>7341.7401528512646</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>12228.571428571429</v>
+      </c>
+      <c r="G6" s="2">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="H6" s="4">
+        <v>15000</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="1"/>
+        <v>19886.831275720164</v>
+      </c>
+      <c r="J6" s="4">
+        <v>12657.142857142857</v>
+      </c>
+      <c r="K6">
+        <v>4571.4285714285706</v>
+      </c>
+      <c r="L6">
+        <v>17682.613168724245</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>45925</v>
+      </c>
+      <c r="B7">
+        <v>1.6237697368421053</v>
+      </c>
+      <c r="C7">
+        <v>0.32475657894736842</v>
+      </c>
+      <c r="D7" s="2">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="E7" s="2">
+        <v>4456.0258671369784</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>9342.8571428571431</v>
+      </c>
+      <c r="G7" s="2">
+        <v>4886.8312757201647</v>
+      </c>
+      <c r="H7" s="4">
+        <v>15000</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="1"/>
+        <v>19886.831275720164</v>
+      </c>
+      <c r="J7" s="4">
+        <v>12000</v>
+      </c>
+      <c r="K7">
+        <v>1914.2857142857138</v>
+      </c>
+      <c r="L7">
+        <v>19611.623209876507</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>45955</v>
+      </c>
+      <c r="B8">
+        <v>1.7219534883720931</v>
+      </c>
+      <c r="C8">
+        <v>1.7219534883720931</v>
+      </c>
+      <c r="D8" s="2">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="E8" s="2">
+        <v>10546.924603174602</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>13314.285714285714</v>
+      </c>
+      <c r="G8" s="2">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="H8" s="4">
+        <v>15000</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="1"/>
+        <v>17767.361111111109</v>
+      </c>
+      <c r="J8" s="4">
+        <v>11714.285714285714</v>
+      </c>
+      <c r="K8">
+        <v>3514.2857142857138</v>
+      </c>
+      <c r="L8">
+        <v>17168.207572016425</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>45986</v>
+      </c>
+      <c r="B9">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="C9">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="D9" s="2">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="E9" s="2">
+        <v>7346.9246031746025</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>10114.285714285714</v>
+      </c>
+      <c r="G9" s="2">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="H9" s="4">
+        <v>3088.8718871251899</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="1"/>
+        <v>5856.2329982363008</v>
+      </c>
+      <c r="J9" s="4">
+        <v>9342.8571428571431</v>
+      </c>
+      <c r="K9">
+        <v>4285.7142857142844</v>
+      </c>
+      <c r="L9">
+        <v>13698.428765432065</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>46016</v>
+      </c>
+      <c r="B10">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="C10">
+        <v>2.2939030624099632</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="E10" s="2">
+        <v>6461.210317460318</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>9228.5714285714294</v>
+      </c>
+      <c r="G10" s="2">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="1"/>
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="J10" s="4">
+        <v>9085.7142857142862</v>
+      </c>
+      <c r="K10">
+        <v>4428.5714285714275</v>
+      </c>
+      <c r="L10">
+        <v>9167.6931687242432</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>46047</v>
+      </c>
+      <c r="B11">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="C11">
+        <v>0.28673497839118917</v>
+      </c>
+      <c r="D11" s="2">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="E11" s="2">
+        <v>3404.0674603174602</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>6171.4285714285716</v>
+      </c>
+      <c r="G11" s="2">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="1"/>
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="J11" s="4">
+        <v>9028.5714285714294</v>
+      </c>
+      <c r="K11">
+        <v>1571.4285714285706</v>
+      </c>
+      <c r="L11">
+        <v>8302.0810288065477</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>46078</v>
+      </c>
+      <c r="B12">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="C12">
+        <v>1.4336865095961708</v>
+      </c>
+      <c r="D12" s="2">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="E12" s="2">
+        <v>4975.4960317460318</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>7742.8571428571431</v>
+      </c>
+      <c r="G12" s="2">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="1"/>
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="J12" s="4">
+        <v>7685.7142857142853</v>
+      </c>
+      <c r="K12">
+        <v>1628.5714285714284</v>
+      </c>
+      <c r="L12">
+        <v>5346.7055144032556</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B13">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="C13">
+        <v>1.1469515312049816</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="E13" s="2">
+        <v>4918.353174603174</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>7685.7142857142853</v>
+      </c>
+      <c r="G13" s="2">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="1"/>
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="J13" s="4">
+        <v>7571.4285714285716</v>
+      </c>
+      <c r="K13">
+        <v>1742.8571428571422</v>
+      </c>
+      <c r="L13">
+        <v>2905.7332921810339</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="F17">
+        <f>B2*D2+C2*E2</f>
+        <v>20896.148657136669</v>
+      </c>
+      <c r="G17">
+        <f>B2*G2+C2*H2</f>
+        <v>20896.148657136669</v>
+      </c>
+    </row>
+    <row r="18" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="F18">
+        <f t="shared" ref="F18:F28" si="2">B3*D3+C3*E3</f>
+        <v>7724.5691872427979</v>
+      </c>
+      <c r="G18">
+        <f t="shared" ref="G18:G28" si="3">B3*G3+C3*H3</f>
+        <v>7724.5691872427979</v>
+      </c>
+    </row>
+    <row r="19" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="F19">
+        <f t="shared" si="2"/>
+        <v>22004.599980274761</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="3"/>
+        <v>22004.599980274761</v>
+      </c>
+    </row>
+    <row r="20" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="F20">
+        <f t="shared" si="2"/>
+        <v>15087.875680327363</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="3"/>
+        <v>15087.875680327363</v>
+      </c>
+    </row>
+    <row r="21" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="F21">
+        <f t="shared" si="2"/>
+        <v>15087.875680327363</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="3"/>
+        <v>22549.036102988954</v>
+      </c>
+    </row>
+    <row r="22" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="F22">
+        <f t="shared" si="2"/>
+        <v>9382.2124508802881</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="3"/>
+        <v>12806.437418778429</v>
+      </c>
+    </row>
+    <row r="23" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="F23">
+        <f t="shared" si="2"/>
+        <v>22926.580730897007</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="3"/>
+        <v>30594.569444444445</v>
+      </c>
+    </row>
+    <row r="24" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="F24">
+        <f t="shared" si="2"/>
+        <v>17400.951982633287</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="3"/>
+        <v>10075.257124434422</v>
+      </c>
+    </row>
+    <row r="25" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="F25">
+        <f t="shared" si="2"/>
+        <v>19582.449804878968</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="3"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="26" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="F26">
+        <f t="shared" si="2"/>
+        <v>5737.1248804581701</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="3"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="27" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="F27">
+        <f t="shared" si="2"/>
+        <v>11894.361210045459</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="3"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="28" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="F28">
+        <f t="shared" si="2"/>
+        <v>10402.172375399885</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="3"/>
+        <v>4761.0596707818931</v>
+      </c>
+    </row>
+    <row r="31" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31">
+        <f>SUM(F17:F28)</f>
+        <v>178126.92262050201</v>
+      </c>
+      <c r="G31">
+        <f>SUM(G17:G28)</f>
+        <v>160782.7322787554</v>
+      </c>
+      <c r="H31">
+        <f>100*(F31-G31)/F31</f>
+        <v>9.7369842169778398</v>
+      </c>
+    </row>
+    <row r="32" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32">
+        <f>0.05*SUM(K2:K13)</f>
+        <v>1975.7142857142856</v>
+      </c>
+      <c r="G32">
+        <f>0.05*SUM(L2:L13)</f>
+        <v>6514.3060349794096</v>
+      </c>
+      <c r="H32">
+        <f t="shared" ref="H32:H34" si="4">100*(F32-G32)/F32</f>
+        <v>-229.71903286229841</v>
+      </c>
+    </row>
+    <row r="33" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E34" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34">
+        <f>SUM(F31:F33)</f>
+        <v>180102.6369062163</v>
+      </c>
+      <c r="G34">
+        <f>SUM(G31:G33)</f>
+        <v>167297.03831373481</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="4"/>
+        <v>7.1101671871409993</v>
+      </c>
+    </row>
+    <row r="37" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="F37" s="6">
+        <v>2768</v>
+      </c>
+    </row>
+    <row r="38" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="F38" s="6">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="39" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="F39" s="6">
+        <f>SUM(F37:F38)</f>
+        <v>2798.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{989F71CB-AD47-DE44-A59D-0D4C36249533}">
+  <dimension ref="D6:F9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="6" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6">
+        <v>64623</v>
+      </c>
+      <c r="F6">
+        <f>E6*F7/E7</f>
+        <v>4420.1889132477299</v>
+      </c>
+    </row>
+    <row r="7" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7">
+        <v>59427</v>
+      </c>
+      <c r="F7">
+        <f>E7*F8/E8</f>
+        <v>4064.7844660194178</v>
+      </c>
+    </row>
+    <row r="8" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8">
+        <v>53520</v>
+      </c>
+      <c r="F8">
+        <f>E8*F9/E9</f>
+        <v>3660.7478860006263</v>
+      </c>
+    </row>
+    <row r="9" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9">
+        <v>47895</v>
+      </c>
+      <c r="F9">
+        <v>3276</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>